--- a/docs/training-sources/xlsx_master_23s.xlsx
+++ b/docs/training-sources/xlsx_master_23s.xlsx
@@ -9,8 +9,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vision Macro" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MK — Plan" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Xabi — Plan" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bateria Ejercicios" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changelog" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registros" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planes Confirmados (Claude)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bateria Ejercicios" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changelog" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="55">
+  <fonts count="62">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -381,8 +383,38 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00375623"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
+    </font>
   </fonts>
-  <fills count="26">
+  <fills count="30">
     <fill>
       <patternFill/>
     </fill>
@@ -532,8 +564,28 @@
         <fgColor rgb="00FFEAD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B1D1F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4F4DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -637,11 +689,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="53" fillId="24" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="44" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1260,6 +1326,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="26" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1808,11 +1920,27 @@
           <t>Controlar fatiga — primer HYROX tecnico juntos</t>
         </is>
       </c>
-      <c r="K8" s="17" t="n"/>
-      <c r="L8" s="17" t="n"/>
-      <c r="M8" s="17" t="n"/>
-      <c r="N8" s="17" t="n"/>
-      <c r="O8" s="18" t="n"/>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="L8" s="17" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M8" s="17" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="N8" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O8" s="18" t="inlineStr">
+        <is>
+          <t>D1 Fuerza: Sentadilla 40kg×6 (RPE5 MK, RPE3 Xabi) + Trineo 100kg+peso. D2 Z2: 4km/25min ritmos 6:09→6:05→5:59→6:38 (RPE8). D3 HYROX: sin burpees (suelo quemaba) + sandbag 20kg lungees añadido (RPE7). D4 Sábado: sin registrar.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="33.75" customHeight="1">
       <c r="B9" s="29" t="n">
@@ -2754,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M598"/>
+  <dimension ref="B1:M598"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="1.54296875" customWidth="1" min="1" max="1"/>
@@ -4166,7 +4294,7 @@
       <c r="F52" s="110" t="n"/>
       <c r="G52" s="137" t="inlineStr">
         <is>
-          <t>800m Run → 1000m Row TOTAL (pareja, ~50% cada uno) → 30 Lunges</t>
+          <t>800m Run → 500m Remo → 30 Lunges</t>
         </is>
       </c>
       <c r="H52" s="110" t="n"/>
@@ -4562,7 +4690,7 @@
       <c r="F66" s="110" t="n"/>
       <c r="G66" s="137" t="inlineStr">
         <is>
-          <t>800m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa)</t>
+          <t>800m Run → 500m Ski Erg → 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H66" s="110" t="n"/>
@@ -4580,7 +4708,7 @@
       <c r="F67" s="110" t="n"/>
       <c r="G67" s="137" t="inlineStr">
         <is>
-          <t>→ 1000m Row TOTAL (pareja, ~50% cada uno) → 30 Lunges → 40 Burpees lentos → 50 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>→ 500m Remo → 30 Lunges → 40 Burpees lentos → 25 Wall Balls</t>
         </is>
       </c>
       <c r="H67" s="110" t="n"/>
@@ -4958,7 +5086,7 @@
       <c r="F80" s="110" t="n"/>
       <c r="G80" s="137" t="inlineStr">
         <is>
-          <t>800m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 25 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>800m Run → 500m Ski Erg → 12 Wall Balls</t>
         </is>
       </c>
       <c r="H80" s="110" t="n"/>
@@ -4976,7 +5104,7 @@
       <c r="F81" s="110" t="n"/>
       <c r="G81" s="137" t="inlineStr">
         <is>
-          <t>→ 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa) → 800m Row TOTAL (pareja, ~50% cada uno) → 30 Lunges → 30 Burpees</t>
+          <t>→ 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces) → 400m Remo → 30 Lunges → 30 Burpees</t>
         </is>
       </c>
       <c r="H81" s="110" t="n"/>
@@ -5354,7 +5482,7 @@
       <c r="F94" s="110" t="n"/>
       <c r="G94" s="137" t="inlineStr">
         <is>
-          <t>600m Run → 1000m Row TOTAL (pareja, ~50% cada uno) → 20 WB TOTAL (pareja, ~50% cada uno) → 20m Sled Push (pareja: un atleta lo completa)</t>
+          <t>600m Run → 500m Remo → 10 Wall Balls → 20m Sled Push (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H94" s="110" t="n"/>
@@ -5372,7 +5500,7 @@
       <c r="F95" s="110" t="n"/>
       <c r="G95" s="137" t="inlineStr">
         <is>
-          <t>→ 20m Sled Pull (pareja: un atleta lo completa) → 20 Burpees → 30 Lunges → 600m Run</t>
+          <t>→ 20m Sled Pull (completo — tú lo haces) → 20 Burpees → 30 Lunges → 600m Run</t>
         </is>
       </c>
       <c r="H95" s="110" t="n"/>
@@ -5750,7 +5878,7 @@
       <c r="F108" s="110" t="n"/>
       <c r="G108" s="137" t="inlineStr">
         <is>
-          <t>800m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 40 Lunges</t>
+          <t>800m Run → 500m Ski Erg → 40 Lunges</t>
         </is>
       </c>
       <c r="H108" s="110" t="n"/>
@@ -6146,7 +6274,7 @@
       <c r="F122" s="110" t="n"/>
       <c r="G122" s="137" t="inlineStr">
         <is>
-          <t>800m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa)</t>
+          <t>800m Run → 500m Ski Erg → 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H122" s="110" t="n"/>
@@ -6164,7 +6292,7 @@
       <c r="F123" s="110" t="n"/>
       <c r="G123" s="137" t="inlineStr">
         <is>
-          <t>→ 1000m Row TOTAL (pareja, ~50% cada uno) → 30 Lunges → 30 Burpees → 50 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>→ 500m Remo → 30 Lunges → 30 Burpees → 25 Wall Balls</t>
         </is>
       </c>
       <c r="H123" s="110" t="n"/>
@@ -6736,7 +6864,7 @@
       <c r="F147" s="82" t="n"/>
       <c r="G147" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 25m Sled Push (pareja: un atleta lo completa) → 25m Sled Pull (pareja: un atleta lo completa)</t>
+          <t>1000m Run → 500m Ski Erg → 25m Sled Push (completo — tú lo haces) → 25m Sled Pull (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H147" s="82" t="n"/>
@@ -6754,7 +6882,7 @@
       <c r="F148" s="82" t="n"/>
       <c r="G148" s="83" t="inlineStr">
         <is>
-          <t>→ 60m Burpee BBJ → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 50m Lunges (pareja: un atleta lo completa) → 50 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>→ 60m Burpee BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 50m Lunges (completo — tú lo haces) → 25 Wall Balls</t>
         </is>
       </c>
       <c r="H148" s="82" t="n"/>
@@ -7238,9 +7366,11 @@
       <c r="D167" s="82" t="n"/>
       <c r="E167" s="82" t="n"/>
       <c r="F167" s="82" t="n"/>
-      <c r="G167" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G167" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 10 KB Swing (F20) + 8 Thruster barra/KB (F17) + 200m Remo
+Desc 90'' entre rondas
+KB Swing: 16-20kg · Thruster: barra vacía o KB ligero</t>
         </is>
       </c>
       <c r="H167" s="82" t="n"/>
@@ -7452,7 +7582,7 @@
       <c r="F177" s="82" t="n"/>
       <c r="G177" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 50m Sled Push (pareja: un atleta lo completa) → 50m Sled Pull (pareja: un atleta lo completa)</t>
+          <t>1000m Run → 500m Ski Erg → 50m Sled Push (completo — tú lo haces) → 50m Sled Pull (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H177" s="82" t="n"/>
@@ -7470,7 +7600,7 @@
       <c r="F178" s="82" t="n"/>
       <c r="G178" s="83" t="inlineStr">
         <is>
-          <t>→ 80m BBJ TOTAL (pareja, ~50% cada uno) → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 80m Lunges (pareja: un atleta lo completa) → 80 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>→ 40m BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 80m Lunges (completo — tú lo haces) → 40 Wall Balls</t>
         </is>
       </c>
       <c r="H178" s="82" t="n"/>
@@ -7954,9 +8084,11 @@
       <c r="D197" s="82" t="n"/>
       <c r="E197" s="82" t="n"/>
       <c r="F197" s="82" t="n"/>
-      <c r="G197" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G197" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 8 Push Press (F18) + 10 Burpee to Plate (H09) + 200m Remo
+Desc 90'' entre rondas
+Push Press: barra ligera · Burpee to Plate: disco en suelo</t>
         </is>
       </c>
       <c r="H197" s="82" t="n"/>
@@ -8168,7 +8300,7 @@
       <c r="F207" s="82" t="n"/>
       <c r="G207" s="83" t="inlineStr">
         <is>
-          <t>500m Ski TOTAL (pareja, ~50% cada uno) → 500m Row TOTAL (pareja, ~50% cada uno) → 20 WB TOTAL (pareja, ~50% cada uno) → 20 Lunges → 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa) → 500m Run</t>
+          <t>250m Ski Erg → 250m Remo → 10 Wall Balls → 20 Lunges → 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces) → 500m Run</t>
         </is>
       </c>
       <c r="H207" s="82" t="n"/>
@@ -8866,7 +8998,7 @@
       <c r="F236" s="82" t="n"/>
       <c r="G236" s="83" t="inlineStr">
         <is>
-          <t>750m Ski TOTAL (pareja, ~50% cada uno) → 15 WB TOTAL (pareja, ~50% cada uno) → 500m Run → 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa) → 750m Row TOTAL (pareja, ~50% cada uno) → 30 Lunges → 40 WB</t>
+          <t>375m Ski Erg → 7 Wall Balls → 500m Run → 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces) → 375m Remo → 30 Lunges → 40 WB</t>
         </is>
       </c>
       <c r="H236" s="82" t="n"/>
@@ -9350,9 +9482,11 @@
       <c r="D255" s="82" t="n"/>
       <c r="E255" s="82" t="n"/>
       <c r="F255" s="82" t="n"/>
-      <c r="G255" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G255" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 12 KB Swing (F20) + 8 Thruster (F17) + 200m Remo
+Desc 90'' entre rondas
+KB Swing: 20kg · Thruster: barra 20-30kg</t>
         </is>
       </c>
       <c r="H255" s="82" t="n"/>
@@ -9564,7 +9698,7 @@
       <c r="F265" s="82" t="n"/>
       <c r="G265" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 50m Sled Push (pareja: un atleta lo completa) → 50m Sled Pull (pareja: un atleta lo completa) → 80m BBJ TOTAL (pareja, ~50% cada uno) → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 100m Lunges (pareja: un atleta lo completa) → 100 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>1000m Run → 500m Ski Erg → 50m Sled Push (completo — tú lo haces) → 50m Sled Pull (completo — tú lo haces) → 40m BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 100m Lunges (completo — tú lo haces) → 50 Wall Balls</t>
         </is>
       </c>
       <c r="H265" s="82" t="n"/>
@@ -9886,9 +10020,12 @@
       <c r="D279" s="84" t="n"/>
       <c r="E279" s="84" t="n"/>
       <c r="F279" s="84" t="n"/>
-      <c r="G279" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G279" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×8 KB Swing (F20) 20kg — explosivo
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H279" s="84" t="n"/>
@@ -10228,9 +10365,11 @@
       <c r="D292" s="82" t="n"/>
       <c r="E292" s="82" t="n"/>
       <c r="F292" s="82" t="n"/>
-      <c r="G292" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G292" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 8 Push Press (F18) + 10 Burpee to Plate (H09) + 200m Remo
+Desc 90'' entre rondas
+Push Press: carga moderada (60-70% PM) · Burpee to Plate: disco 20kg</t>
         </is>
       </c>
       <c r="H292" s="82" t="n"/>
@@ -10442,7 +10581,7 @@
       <c r="F302" s="82" t="n"/>
       <c r="G302" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 50m Sled Push (pareja: un atleta lo completa) → 50m Sled Pull (pareja: un atleta lo completa) → 80m BBJ TOTAL (pareja, ~50% cada uno) → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 100m Lunges (pareja: un atleta lo completa) → 100 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>1000m Run → 500m Ski Erg → 50m Sled Push (completo — tú lo haces) → 50m Sled Pull (completo — tú lo haces) → 40m BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 100m Lunges (completo — tú lo haces) → 50 Wall Balls</t>
         </is>
       </c>
       <c r="H302" s="82" t="n"/>
@@ -10764,9 +10903,12 @@
       <c r="D316" s="84" t="n"/>
       <c r="E316" s="84" t="n"/>
       <c r="F316" s="84" t="n"/>
-      <c r="G316" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G316" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×6 Push Press (F18) ligero — técnica
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H316" s="84" t="n"/>
@@ -11106,9 +11248,11 @@
       <c r="D329" s="82" t="n"/>
       <c r="E329" s="82" t="n"/>
       <c r="F329" s="82" t="n"/>
-      <c r="G329" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G329" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 12 KB Swing (F20) + 6 Devils Press (F21) + 200m Remo
+Desc 90'' entre rondas
+KB Swing: 20-24kg · Devils Press: mancuernas ligeras (7.5-10kg)</t>
         </is>
       </c>
       <c r="H329" s="82" t="n"/>
@@ -11300,9 +11444,10 @@
       <c r="D338" s="82" t="n"/>
       <c r="E338" s="82" t="n"/>
       <c r="F338" s="82" t="n"/>
-      <c r="G338" s="83" t="inlineStr">
-        <is>
-          <t>HYROX potencia — series de estaciones:</t>
+      <c r="G338" s="231" t="inlineStr">
+        <is>
+          <t>HYROX potencia — series de estaciones:
+⚡ SOBRECARGA: Esta semana entrena con carga superior a competición — WB +2kg extra · Farmer Carry +4kg/lado · Sled con disco adicional. Objetivo: hacer que la comp parezca ligera.</t>
         </is>
       </c>
       <c r="H338" s="82" t="n"/>
@@ -11320,7 +11465,7 @@
       <c r="F339" s="82" t="n"/>
       <c r="G339" s="83" t="inlineStr">
         <is>
-          <t>4×(500m Run → 500m Ski TOTAL (pareja, ~50% cada uno) → 500m Row TOTAL (pareja, ~50% cada uno)) · Desc 3'</t>
+          <t>4×(500m Run → 250m Ski Erg → 250m Remo) · Desc 3'</t>
         </is>
       </c>
       <c r="H339" s="82" t="n"/>
@@ -11338,7 +11483,7 @@
       <c r="F340" s="82" t="n"/>
       <c r="G340" s="83" t="inlineStr">
         <is>
-          <t>Luego: 3×(20m Sled Push (pareja: un atleta lo completa)+Pull → 20 BBJ → 40m Farmer Carry (pareja: un atleta lo completa))</t>
+          <t>Luego: 3×(20m Sled Push (completo — tú lo haces)+Pull → 20 BBJ → 40m Farmer Carry (completo — tú lo haces))</t>
         </is>
       </c>
       <c r="H340" s="82" t="n"/>
@@ -11660,9 +11805,12 @@
       <c r="D354" s="84" t="n"/>
       <c r="E354" s="84" t="n"/>
       <c r="F354" s="84" t="n"/>
-      <c r="G354" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G354" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×8 KB Swing (F20) 24kg + 3×5/lado Snatch KB (F19) 12kg
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H354" s="84" t="n"/>
@@ -12002,9 +12150,11 @@
       <c r="D367" s="82" t="n"/>
       <c r="E367" s="82" t="n"/>
       <c r="F367" s="82" t="n"/>
-      <c r="G367" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G367" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 10 KB Swing (F20) + 10 Burpee to Plate (H09) + 200m Remo
+Desc 90'' entre rondas
+KB Swing: 20-24kg · Burpee to Plate: disco 20kg</t>
         </is>
       </c>
       <c r="H367" s="82" t="n"/>
@@ -12196,9 +12346,10 @@
       <c r="D376" s="82" t="n"/>
       <c r="E376" s="82" t="n"/>
       <c r="F376" s="82" t="n"/>
-      <c r="G376" s="83" t="inlineStr">
-        <is>
-          <t>SIMULACRO COMPLETO 90%:</t>
+      <c r="G376" s="231" t="inlineStr">
+        <is>
+          <t>SIMULACRO COMPLETO 90%:
+⚡ SOBRECARGA: Esta semana entrena con carga superior a competición — WB +2kg extra · Farmer Carry +4kg/lado · Sled con disco adicional. Objetivo: hacer que la comp parezca ligera.</t>
         </is>
       </c>
       <c r="H376" s="82" t="n"/>
@@ -12216,7 +12367,7 @@
       <c r="F377" s="82" t="n"/>
       <c r="G377" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 50m Sled Push (pareja: un atleta lo completa) → 50m Sled Pull (pareja: un atleta lo completa)</t>
+          <t>1000m Run → 500m Ski Erg → 50m Sled Push (completo — tú lo haces) → 50m Sled Pull (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H377" s="82" t="n"/>
@@ -12234,7 +12385,7 @@
       <c r="F378" s="82" t="n"/>
       <c r="G378" s="83" t="inlineStr">
         <is>
-          <t>→ 80m BBJ TOTAL (pareja, ~50% cada uno) → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 100m Lunges (pareja: un atleta lo completa) → 100 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>→ 40m BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 100m Lunges (completo — tú lo haces) → 50 Wall Balls</t>
         </is>
       </c>
       <c r="H378" s="82" t="n"/>
@@ -12556,9 +12707,12 @@
       <c r="D392" s="84" t="n"/>
       <c r="E392" s="84" t="n"/>
       <c r="F392" s="84" t="n"/>
-      <c r="G392" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G392" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×6 Push Press (F18) moderado
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H392" s="84" t="n"/>
@@ -13112,7 +13266,7 @@
       <c r="F415" s="82" t="n"/>
       <c r="G415" s="83" t="inlineStr">
         <is>
-          <t>500m Ski TOTAL (pareja, ~50% cada uno) → 500m Row TOTAL (pareja, ~50% cada uno) → 20 WB TOTAL (pareja, ~50% cada uno) → 20 Lunges → 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa) → 500m Run</t>
+          <t>250m Ski Erg → 250m Remo → 10 Wall Balls → 20 Lunges → 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces) → 500m Run</t>
         </is>
       </c>
       <c r="H415" s="82" t="n"/>
@@ -13776,9 +13930,11 @@
       <c r="D442" s="82" t="n"/>
       <c r="E442" s="82" t="n"/>
       <c r="F442" s="82" t="n"/>
-      <c r="G442" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G442" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 8 Push Press (F18) + 5 Snatch KB/lado (F19) + 200m Remo
+Desc 90'' entre rondas
+Push Press: carga alta · Snatch KB: técnica limpia, 16kg</t>
         </is>
       </c>
       <c r="H442" s="82" t="n"/>
@@ -13990,7 +14146,7 @@
       <c r="F452" s="82" t="n"/>
       <c r="G452" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 50m Sled Push (pareja: un atleta lo completa) → 50m Sled Pull (pareja: un atleta lo completa) → 80m BBJ TOTAL (pareja, ~50% cada uno) → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 100m Lunges (pareja: un atleta lo completa) → 100 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>1000m Run → 500m Ski Erg → 50m Sled Push (completo — tú lo haces) → 50m Sled Pull (completo — tú lo haces) → 40m BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 100m Lunges (completo — tú lo haces) → 50 Wall Balls</t>
         </is>
       </c>
       <c r="H452" s="82" t="n"/>
@@ -14312,9 +14468,12 @@
       <c r="D466" s="84" t="n"/>
       <c r="E466" s="84" t="n"/>
       <c r="F466" s="84" t="n"/>
-      <c r="G466" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G466" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×8 KB Swing (F20) 24kg + 3×6 Push Press (F18)
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H466" s="84" t="n"/>
@@ -14654,9 +14813,11 @@
       <c r="D479" s="82" t="n"/>
       <c r="E479" s="82" t="n"/>
       <c r="F479" s="82" t="n"/>
-      <c r="G479" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G479" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 12 KB Swing (F20) + 10 Burpee to Plate (H09) + 200m Remo
+Desc 90'' entre rondas
+KB Swing: 24kg · Burpee to Plate: máxima potencia</t>
         </is>
       </c>
       <c r="H479" s="82" t="n"/>
@@ -14848,9 +15009,10 @@
       <c r="D488" s="82" t="n"/>
       <c r="E488" s="82" t="n"/>
       <c r="F488" s="82" t="n"/>
-      <c r="G488" s="83" t="inlineStr">
-        <is>
-          <t>SIMULACRO COMPLETO 100%:</t>
+      <c r="G488" s="231" t="inlineStr">
+        <is>
+          <t>SIMULACRO COMPLETO 100%:
+⚡ SOBRECARGA: Esta semana entrena con carga superior a competición — WB +2kg extra · Farmer Carry +4kg/lado · Sled con disco adicional. Objetivo: hacer que la comp parezca ligera.</t>
         </is>
       </c>
       <c r="H488" s="82" t="n"/>
@@ -14868,7 +15030,7 @@
       <c r="F489" s="82" t="n"/>
       <c r="G489" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 50m Sled Push (pareja: un atleta lo completa) → 50m Sled Pull (pareja: un atleta lo completa)</t>
+          <t>1000m Run → 500m Ski Erg → 50m Sled Push (completo — tú lo haces) → 50m Sled Pull (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H489" s="82" t="n"/>
@@ -14886,7 +15048,7 @@
       <c r="F490" s="82" t="n"/>
       <c r="G490" s="83" t="inlineStr">
         <is>
-          <t>→ 80m BBJ TOTAL (pareja, ~50% cada uno) → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 100m Lunges (pareja: un atleta lo completa) → 100 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>→ 40m BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 100m Lunges (completo — tú lo haces) → 50 Wall Balls</t>
         </is>
       </c>
       <c r="H490" s="82" t="n"/>
@@ -15208,9 +15370,12 @@
       <c r="D504" s="84" t="n"/>
       <c r="E504" s="84" t="n"/>
       <c r="F504" s="84" t="n"/>
-      <c r="G504" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G504" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×8 KB Swing (F20) 24kg — pico
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H504" s="84" t="n"/>
@@ -15550,9 +15715,11 @@
       <c r="D517" s="82" t="n"/>
       <c r="E517" s="82" t="n"/>
       <c r="F517" s="82" t="n"/>
-      <c r="G517" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G517" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 8 Push Press (F18) + 10 Wall Ball + 200m Remo
+Desc 90'' entre rondas
+Push Press: peso técnico · Wall Ball: ritmo comp</t>
         </is>
       </c>
       <c r="H517" s="82" t="n"/>
@@ -15764,7 +15931,7 @@
       <c r="F527" s="82" t="n"/>
       <c r="G527" s="83" t="inlineStr">
         <is>
-          <t>500m Ski TOTAL (pareja, ~50% cada uno) → 20 WB TOTAL (pareja, ~50% cada uno) → 500m Run → 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa) → 500m Row TOTAL (pareja, ~50% cada uno) → 30 Lunges → 500m Run</t>
+          <t>250m Ski Erg → 10 Wall Balls → 500m Run → 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces) → 250m Remo → 30 Lunges → 500m Run</t>
         </is>
       </c>
       <c r="H527" s="82" t="n"/>
@@ -16086,9 +16253,12 @@
       <c r="D541" s="84" t="n"/>
       <c r="E541" s="84" t="n"/>
       <c r="F541" s="84" t="n"/>
-      <c r="G541" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G541" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×6 Push Press (F18) — técnica fina
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H541" s="84" t="n"/>
@@ -16410,9 +16580,11 @@
       <c r="D553" s="82" t="n"/>
       <c r="E553" s="82" t="n"/>
       <c r="F553" s="82" t="n"/>
-      <c r="G553" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G553" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 8 Push Press (F18) + 10 Wall Ball + 200m Remo
+Desc 90'' entre rondas
+Push Press: peso técnico · Wall Ball: ritmo comp</t>
         </is>
       </c>
       <c r="H553" s="82" t="n"/>
@@ -16628,7 +16800,7 @@
       <c r="F563" s="82" t="n"/>
       <c r="G563" s="83" t="inlineStr">
         <is>
-          <t>500m Run → 500m Ski TOTAL (pareja, ~50% cada uno) → 500m Row TOTAL (pareja, ~50% cada uno)</t>
+          <t>500m Run → 250m Ski Erg → 250m Remo</t>
         </is>
       </c>
       <c r="H563" s="82" t="n"/>
@@ -16646,7 +16818,7 @@
       <c r="F564" s="82" t="n"/>
       <c r="G564" s="83" t="inlineStr">
         <is>
-          <t>→ 10m Sled Push (pareja: un atleta lo completa) → 10m Sled Pull (pareja: un atleta lo completa) → 10 WB TOTAL (pareja, ~50% cada uno) → 10 Lunges</t>
+          <t>→ 10m Sled Push (completo — tú lo haces) → 10m Sled Pull (completo — tú lo haces) → 5 Wall Balls → 10 Lunges</t>
         </is>
       </c>
       <c r="H564" s="82" t="n"/>
@@ -17168,7 +17340,7 @@
       <c r="F583" s="110" t="n"/>
       <c r="G583" s="137" t="inlineStr">
         <is>
-          <t>500m Run → 500m Ski TOTAL (pareja, ~50% cada uno) → 500m Row TOTAL (pareja, ~50% cada uno)</t>
+          <t>500m Run → 250m Ski Erg → 250m Remo</t>
         </is>
       </c>
       <c r="H583" s="110" t="n"/>
@@ -17186,7 +17358,7 @@
       <c r="F584" s="110" t="n"/>
       <c r="G584" s="137" t="inlineStr">
         <is>
-          <t>→ 10m Sled Push (pareja: un atleta lo completa) → 10m Sled Pull (pareja: un atleta lo completa) → 10 WB TOTAL (pareja, ~50% cada uno) → 10 Lunges</t>
+          <t>→ 10m Sled Push (completo — tú lo haces) → 10m Sled Pull (completo — tú lo haces) → 5 Wall Balls → 10 Lunges</t>
         </is>
       </c>
       <c r="H584" s="110" t="n"/>
@@ -17632,7 +17804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M598"/>
+  <dimension ref="B1:M598"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="1.54296875" customWidth="1" min="1" max="1"/>
@@ -19046,7 +19218,7 @@
       <c r="F52" s="110" t="n"/>
       <c r="G52" s="137" t="inlineStr">
         <is>
-          <t>800m Run → 1000m Row TOTAL (pareja, ~50% cada uno) → 30 Lunges</t>
+          <t>800m Run → 500m Remo → 30 Lunges</t>
         </is>
       </c>
       <c r="H52" s="110" t="n"/>
@@ -19442,7 +19614,7 @@
       <c r="F66" s="110" t="n"/>
       <c r="G66" s="137" t="inlineStr">
         <is>
-          <t>800m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa)</t>
+          <t>800m Run → 500m Ski Erg → 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H66" s="110" t="n"/>
@@ -19460,7 +19632,7 @@
       <c r="F67" s="110" t="n"/>
       <c r="G67" s="137" t="inlineStr">
         <is>
-          <t>→ 1000m Row TOTAL (pareja, ~50% cada uno) → 30 Lunges → 40 Burpees lentos → 50 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>→ 500m Remo → 30 Lunges → 40 Burpees lentos → 25 Wall Balls</t>
         </is>
       </c>
       <c r="H67" s="110" t="n"/>
@@ -19838,7 +20010,7 @@
       <c r="F80" s="110" t="n"/>
       <c r="G80" s="137" t="inlineStr">
         <is>
-          <t>800m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 25 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>800m Run → 500m Ski Erg → 12 Wall Balls</t>
         </is>
       </c>
       <c r="H80" s="110" t="n"/>
@@ -19856,7 +20028,7 @@
       <c r="F81" s="110" t="n"/>
       <c r="G81" s="137" t="inlineStr">
         <is>
-          <t>→ 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa) → 800m Row TOTAL (pareja, ~50% cada uno) → 30 Lunges → 30 Burpees</t>
+          <t>→ 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces) → 400m Remo → 30 Lunges → 30 Burpees</t>
         </is>
       </c>
       <c r="H81" s="110" t="n"/>
@@ -20234,7 +20406,7 @@
       <c r="F94" s="110" t="n"/>
       <c r="G94" s="137" t="inlineStr">
         <is>
-          <t>600m Run → 1000m Row TOTAL (pareja, ~50% cada uno) → 20 WB TOTAL (pareja, ~50% cada uno) → 20m Sled Push (pareja: un atleta lo completa)</t>
+          <t>600m Run → 500m Remo → 10 Wall Balls → 20m Sled Push (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H94" s="110" t="n"/>
@@ -20252,7 +20424,7 @@
       <c r="F95" s="110" t="n"/>
       <c r="G95" s="137" t="inlineStr">
         <is>
-          <t>→ 20m Sled Pull (pareja: un atleta lo completa) → 20 Burpees → 30 Lunges → 600m Run</t>
+          <t>→ 20m Sled Pull (completo — tú lo haces) → 20 Burpees → 30 Lunges → 600m Run</t>
         </is>
       </c>
       <c r="H95" s="110" t="n"/>
@@ -20630,7 +20802,7 @@
       <c r="F108" s="110" t="n"/>
       <c r="G108" s="137" t="inlineStr">
         <is>
-          <t>800m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 40 Lunges</t>
+          <t>800m Run → 500m Ski Erg → 40 Lunges</t>
         </is>
       </c>
       <c r="H108" s="110" t="n"/>
@@ -21026,7 +21198,7 @@
       <c r="F122" s="110" t="n"/>
       <c r="G122" s="137" t="inlineStr">
         <is>
-          <t>800m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa)</t>
+          <t>800m Run → 500m Ski Erg → 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H122" s="110" t="n"/>
@@ -21044,7 +21216,7 @@
       <c r="F123" s="110" t="n"/>
       <c r="G123" s="137" t="inlineStr">
         <is>
-          <t>→ 1000m Row TOTAL (pareja, ~50% cada uno) → 30 Lunges → 30 Burpees → 50 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>→ 500m Remo → 30 Lunges → 30 Burpees → 25 Wall Balls</t>
         </is>
       </c>
       <c r="H123" s="110" t="n"/>
@@ -21616,7 +21788,7 @@
       <c r="F147" s="82" t="n"/>
       <c r="G147" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 25m Sled Push (pareja: un atleta lo completa) → 25m Sled Pull (pareja: un atleta lo completa)</t>
+          <t>1000m Run → 500m Ski Erg → 25m Sled Push (completo — tú lo haces) → 25m Sled Pull (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H147" s="82" t="n"/>
@@ -21634,7 +21806,7 @@
       <c r="F148" s="82" t="n"/>
       <c r="G148" s="83" t="inlineStr">
         <is>
-          <t>→ 60m Burpee BBJ → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 50m Lunges (pareja: un atleta lo completa) → 50 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>→ 60m Burpee BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 50m Lunges (completo — tú lo haces) → 25 Wall Balls</t>
         </is>
       </c>
       <c r="H148" s="82" t="n"/>
@@ -22118,9 +22290,11 @@
       <c r="D167" s="82" t="n"/>
       <c r="E167" s="82" t="n"/>
       <c r="F167" s="82" t="n"/>
-      <c r="G167" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G167" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 10 KB Swing (F20) + 8 Thruster barra/KB (F17) + 200m Remo
+Desc 90'' entre rondas
+KB Swing: 16-20kg · Thruster: barra vacía o KB ligero</t>
         </is>
       </c>
       <c r="H167" s="82" t="n"/>
@@ -22332,7 +22506,7 @@
       <c r="F177" s="82" t="n"/>
       <c r="G177" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 50m Sled Push (pareja: un atleta lo completa) → 50m Sled Pull (pareja: un atleta lo completa)</t>
+          <t>1000m Run → 500m Ski Erg → 50m Sled Push (completo — tú lo haces) → 50m Sled Pull (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H177" s="82" t="n"/>
@@ -22350,7 +22524,7 @@
       <c r="F178" s="82" t="n"/>
       <c r="G178" s="83" t="inlineStr">
         <is>
-          <t>→ 80m BBJ TOTAL (pareja, ~50% cada uno) → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 80m Lunges (pareja: un atleta lo completa) → 80 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>→ 40m BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 80m Lunges (completo — tú lo haces) → 40 Wall Balls</t>
         </is>
       </c>
       <c r="H178" s="82" t="n"/>
@@ -22834,9 +23008,11 @@
       <c r="D197" s="82" t="n"/>
       <c r="E197" s="82" t="n"/>
       <c r="F197" s="82" t="n"/>
-      <c r="G197" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G197" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 8 Push Press (F18) + 10 Burpee to Plate (H09) + 200m Remo
+Desc 90'' entre rondas
+Push Press: barra ligera · Burpee to Plate: disco en suelo</t>
         </is>
       </c>
       <c r="H197" s="82" t="n"/>
@@ -23048,7 +23224,7 @@
       <c r="F207" s="82" t="n"/>
       <c r="G207" s="83" t="inlineStr">
         <is>
-          <t>500m Ski TOTAL (pareja, ~50% cada uno) → 500m Row TOTAL (pareja, ~50% cada uno) → 20 WB TOTAL (pareja, ~50% cada uno) → 20 Lunges → 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa) → 500m Run</t>
+          <t>250m Ski Erg → 250m Remo → 10 Wall Balls → 20 Lunges → 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces) → 500m Run</t>
         </is>
       </c>
       <c r="H207" s="82" t="n"/>
@@ -23746,7 +23922,7 @@
       <c r="F236" s="82" t="n"/>
       <c r="G236" s="83" t="inlineStr">
         <is>
-          <t>750m Ski TOTAL (pareja, ~50% cada uno) → 15 WB TOTAL (pareja, ~50% cada uno) → 500m Run → 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa) → 750m Row TOTAL (pareja, ~50% cada uno) → 30 Lunges → 40 WB</t>
+          <t>375m Ski Erg → 7 Wall Balls → 500m Run → 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces) → 375m Remo → 30 Lunges → 40 WB</t>
         </is>
       </c>
       <c r="H236" s="82" t="n"/>
@@ -24230,9 +24406,11 @@
       <c r="D255" s="82" t="n"/>
       <c r="E255" s="82" t="n"/>
       <c r="F255" s="82" t="n"/>
-      <c r="G255" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G255" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 12 KB Swing (F20) + 8 Thruster (F17) + 200m Remo
+Desc 90'' entre rondas
+KB Swing: 20kg · Thruster: barra 20-30kg</t>
         </is>
       </c>
       <c r="H255" s="82" t="n"/>
@@ -24444,7 +24622,7 @@
       <c r="F265" s="82" t="n"/>
       <c r="G265" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 50m Sled Push (pareja: un atleta lo completa) → 50m Sled Pull (pareja: un atleta lo completa) → 80m BBJ TOTAL (pareja, ~50% cada uno) → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 100m Lunges (pareja: un atleta lo completa) → 100 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>1000m Run → 500m Ski Erg → 50m Sled Push (completo — tú lo haces) → 50m Sled Pull (completo — tú lo haces) → 40m BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 100m Lunges (completo — tú lo haces) → 50 Wall Balls</t>
         </is>
       </c>
       <c r="H265" s="82" t="n"/>
@@ -24766,9 +24944,12 @@
       <c r="D279" s="84" t="n"/>
       <c r="E279" s="84" t="n"/>
       <c r="F279" s="84" t="n"/>
-      <c r="G279" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G279" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×8 KB Swing (F20) 20kg — explosivo
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H279" s="84" t="n"/>
@@ -25108,9 +25289,11 @@
       <c r="D292" s="82" t="n"/>
       <c r="E292" s="82" t="n"/>
       <c r="F292" s="82" t="n"/>
-      <c r="G292" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G292" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 8 Push Press (F18) + 10 Burpee to Plate (H09) + 200m Remo
+Desc 90'' entre rondas
+Push Press: carga moderada (60-70% PM) · Burpee to Plate: disco 20kg</t>
         </is>
       </c>
       <c r="H292" s="82" t="n"/>
@@ -25322,7 +25505,7 @@
       <c r="F302" s="82" t="n"/>
       <c r="G302" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 50m Sled Push (pareja: un atleta lo completa) → 50m Sled Pull (pareja: un atleta lo completa) → 80m BBJ TOTAL (pareja, ~50% cada uno) → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 100m Lunges (pareja: un atleta lo completa) → 100 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>1000m Run → 500m Ski Erg → 50m Sled Push (completo — tú lo haces) → 50m Sled Pull (completo — tú lo haces) → 40m BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 100m Lunges (completo — tú lo haces) → 50 Wall Balls</t>
         </is>
       </c>
       <c r="H302" s="82" t="n"/>
@@ -25644,9 +25827,12 @@
       <c r="D316" s="84" t="n"/>
       <c r="E316" s="84" t="n"/>
       <c r="F316" s="84" t="n"/>
-      <c r="G316" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G316" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×6 Push Press (F18) ligero — técnica
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H316" s="84" t="n"/>
@@ -25986,9 +26172,11 @@
       <c r="D329" s="82" t="n"/>
       <c r="E329" s="82" t="n"/>
       <c r="F329" s="82" t="n"/>
-      <c r="G329" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G329" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 12 KB Swing (F20) + 6 Devils Press (F21) + 200m Remo
+Desc 90'' entre rondas
+KB Swing: 20-24kg · Devils Press: mancuernas ligeras (7.5-10kg)</t>
         </is>
       </c>
       <c r="H329" s="82" t="n"/>
@@ -26180,9 +26368,10 @@
       <c r="D338" s="82" t="n"/>
       <c r="E338" s="82" t="n"/>
       <c r="F338" s="82" t="n"/>
-      <c r="G338" s="83" t="inlineStr">
-        <is>
-          <t>HYROX potencia — series de estaciones:</t>
+      <c r="G338" s="231" t="inlineStr">
+        <is>
+          <t>HYROX potencia — series de estaciones:
+⚡ SOBRECARGA: Esta semana entrena con carga superior a competición — WB +2kg extra · Farmer Carry +4kg/lado · Sled con disco adicional. Objetivo: hacer que la comp parezca ligera.</t>
         </is>
       </c>
       <c r="H338" s="82" t="n"/>
@@ -26200,7 +26389,7 @@
       <c r="F339" s="82" t="n"/>
       <c r="G339" s="83" t="inlineStr">
         <is>
-          <t>4×(500m Run → 500m Ski TOTAL (pareja, ~50% cada uno) → 500m Row TOTAL (pareja, ~50% cada uno)) · Desc 3'</t>
+          <t>4×(500m Run → 250m Ski Erg → 250m Remo) · Desc 3'</t>
         </is>
       </c>
       <c r="H339" s="82" t="n"/>
@@ -26218,7 +26407,7 @@
       <c r="F340" s="82" t="n"/>
       <c r="G340" s="83" t="inlineStr">
         <is>
-          <t>Luego: 3×(20m Sled Push (pareja: un atleta lo completa)+Pull → 20 BBJ → 40m Farmer Carry (pareja: un atleta lo completa))</t>
+          <t>Luego: 3×(20m Sled Push (completo — tú lo haces)+Pull → 20 BBJ → 40m Farmer Carry (completo — tú lo haces))</t>
         </is>
       </c>
       <c r="H340" s="82" t="n"/>
@@ -26540,9 +26729,12 @@
       <c r="D354" s="84" t="n"/>
       <c r="E354" s="84" t="n"/>
       <c r="F354" s="84" t="n"/>
-      <c r="G354" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G354" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×8 KB Swing (F20) 24kg + 3×5/lado Snatch KB (F19) 12kg
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H354" s="84" t="n"/>
@@ -26882,9 +27074,11 @@
       <c r="D367" s="82" t="n"/>
       <c r="E367" s="82" t="n"/>
       <c r="F367" s="82" t="n"/>
-      <c r="G367" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G367" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 10 KB Swing (F20) + 10 Burpee to Plate (H09) + 200m Remo
+Desc 90'' entre rondas
+KB Swing: 20-24kg · Burpee to Plate: disco 20kg</t>
         </is>
       </c>
       <c r="H367" s="82" t="n"/>
@@ -27076,9 +27270,10 @@
       <c r="D376" s="82" t="n"/>
       <c r="E376" s="82" t="n"/>
       <c r="F376" s="82" t="n"/>
-      <c r="G376" s="83" t="inlineStr">
-        <is>
-          <t>SIMULACRO COMPLETO 90%:</t>
+      <c r="G376" s="231" t="inlineStr">
+        <is>
+          <t>SIMULACRO COMPLETO 90%:
+⚡ SOBRECARGA: Esta semana entrena con carga superior a competición — WB +2kg extra · Farmer Carry +4kg/lado · Sled con disco adicional. Objetivo: hacer que la comp parezca ligera.</t>
         </is>
       </c>
       <c r="H376" s="82" t="n"/>
@@ -27096,7 +27291,7 @@
       <c r="F377" s="82" t="n"/>
       <c r="G377" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 50m Sled Push (pareja: un atleta lo completa) → 50m Sled Pull (pareja: un atleta lo completa)</t>
+          <t>1000m Run → 500m Ski Erg → 50m Sled Push (completo — tú lo haces) → 50m Sled Pull (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H377" s="82" t="n"/>
@@ -27114,7 +27309,7 @@
       <c r="F378" s="82" t="n"/>
       <c r="G378" s="83" t="inlineStr">
         <is>
-          <t>→ 80m BBJ TOTAL (pareja, ~50% cada uno) → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 100m Lunges (pareja: un atleta lo completa) → 100 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>→ 40m BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 100m Lunges (completo — tú lo haces) → 50 Wall Balls</t>
         </is>
       </c>
       <c r="H378" s="82" t="n"/>
@@ -27436,9 +27631,12 @@
       <c r="D392" s="84" t="n"/>
       <c r="E392" s="84" t="n"/>
       <c r="F392" s="84" t="n"/>
-      <c r="G392" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G392" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×6 Push Press (F18) moderado
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H392" s="84" t="n"/>
@@ -27992,7 +28190,7 @@
       <c r="F415" s="82" t="n"/>
       <c r="G415" s="83" t="inlineStr">
         <is>
-          <t>500m Ski TOTAL (pareja, ~50% cada uno) → 500m Row TOTAL (pareja, ~50% cada uno) → 20 WB TOTAL (pareja, ~50% cada uno) → 20 Lunges → 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa) → 500m Run</t>
+          <t>250m Ski Erg → 250m Remo → 10 Wall Balls → 20 Lunges → 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces) → 500m Run</t>
         </is>
       </c>
       <c r="H415" s="82" t="n"/>
@@ -28656,9 +28854,11 @@
       <c r="D442" s="82" t="n"/>
       <c r="E442" s="82" t="n"/>
       <c r="F442" s="82" t="n"/>
-      <c r="G442" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G442" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 8 Push Press (F18) + 5 Snatch KB/lado (F19) + 200m Remo
+Desc 90'' entre rondas
+Push Press: carga alta · Snatch KB: técnica limpia, 16kg</t>
         </is>
       </c>
       <c r="H442" s="82" t="n"/>
@@ -28870,7 +29070,7 @@
       <c r="F452" s="82" t="n"/>
       <c r="G452" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 50m Sled Push (pareja: un atleta lo completa) → 50m Sled Pull (pareja: un atleta lo completa) → 80m BBJ TOTAL (pareja, ~50% cada uno) → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 100m Lunges (pareja: un atleta lo completa) → 100 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>1000m Run → 500m Ski Erg → 50m Sled Push (completo — tú lo haces) → 50m Sled Pull (completo — tú lo haces) → 40m BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 100m Lunges (completo — tú lo haces) → 50 Wall Balls</t>
         </is>
       </c>
       <c r="H452" s="82" t="n"/>
@@ -29192,9 +29392,12 @@
       <c r="D466" s="84" t="n"/>
       <c r="E466" s="84" t="n"/>
       <c r="F466" s="84" t="n"/>
-      <c r="G466" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G466" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×8 KB Swing (F20) 24kg + 3×6 Push Press (F18)
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H466" s="84" t="n"/>
@@ -29534,9 +29737,11 @@
       <c r="D479" s="82" t="n"/>
       <c r="E479" s="82" t="n"/>
       <c r="F479" s="82" t="n"/>
-      <c r="G479" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G479" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 12 KB Swing (F20) + 10 Burpee to Plate (H09) + 200m Remo
+Desc 90'' entre rondas
+KB Swing: 24kg · Burpee to Plate: máxima potencia</t>
         </is>
       </c>
       <c r="H479" s="82" t="n"/>
@@ -29728,9 +29933,10 @@
       <c r="D488" s="82" t="n"/>
       <c r="E488" s="82" t="n"/>
       <c r="F488" s="82" t="n"/>
-      <c r="G488" s="83" t="inlineStr">
-        <is>
-          <t>SIMULACRO COMPLETO 100%:</t>
+      <c r="G488" s="231" t="inlineStr">
+        <is>
+          <t>SIMULACRO COMPLETO 100%:
+⚡ SOBRECARGA: Esta semana entrena con carga superior a competición — WB +2kg extra · Farmer Carry +4kg/lado · Sled con disco adicional. Objetivo: hacer que la comp parezca ligera.</t>
         </is>
       </c>
       <c r="H488" s="82" t="n"/>
@@ -29748,7 +29954,7 @@
       <c r="F489" s="82" t="n"/>
       <c r="G489" s="83" t="inlineStr">
         <is>
-          <t>1000m Run → 1000m Ski TOTAL (pareja, ~50% cada uno) → 50m Sled Push (pareja: un atleta lo completa) → 50m Sled Pull (pareja: un atleta lo completa)</t>
+          <t>1000m Run → 500m Ski Erg → 50m Sled Push (completo — tú lo haces) → 50m Sled Pull (completo — tú lo haces)</t>
         </is>
       </c>
       <c r="H489" s="82" t="n"/>
@@ -29766,7 +29972,7 @@
       <c r="F490" s="82" t="n"/>
       <c r="G490" s="83" t="inlineStr">
         <is>
-          <t>→ 80m BBJ TOTAL (pareja, ~50% cada uno) → 1000m Row TOTAL (pareja, ~50% cada uno) → 200m Farmer Carry (pareja: un atleta lo completa) → 100m Lunges (pareja: un atleta lo completa) → 100 WB TOTAL (pareja, ~50% cada uno)</t>
+          <t>→ 40m BBJ → 500m Remo → 200m Farmer Carry (completo — tú lo haces) → 100m Lunges (completo — tú lo haces) → 50 Wall Balls</t>
         </is>
       </c>
       <c r="H490" s="82" t="n"/>
@@ -30088,9 +30294,12 @@
       <c r="D504" s="84" t="n"/>
       <c r="E504" s="84" t="n"/>
       <c r="F504" s="84" t="n"/>
-      <c r="G504" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G504" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×8 KB Swing (F20) 24kg — pico
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H504" s="84" t="n"/>
@@ -30430,9 +30639,11 @@
       <c r="D517" s="82" t="n"/>
       <c r="E517" s="82" t="n"/>
       <c r="F517" s="82" t="n"/>
-      <c r="G517" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G517" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 8 Push Press (F18) + 10 Wall Ball + 200m Remo
+Desc 90'' entre rondas
+Push Press: peso técnico · Wall Ball: ritmo comp</t>
         </is>
       </c>
       <c r="H517" s="82" t="n"/>
@@ -30644,7 +30855,7 @@
       <c r="F527" s="82" t="n"/>
       <c r="G527" s="83" t="inlineStr">
         <is>
-          <t>500m Ski TOTAL (pareja, ~50% cada uno) → 20 WB TOTAL (pareja, ~50% cada uno) → 500m Run → 20m Sled Push (pareja: un atleta lo completa) → 20m Sled Pull (pareja: un atleta lo completa) → 500m Row TOTAL (pareja, ~50% cada uno) → 30 Lunges → 500m Run</t>
+          <t>250m Ski Erg → 10 Wall Balls → 500m Run → 20m Sled Push (completo — tú lo haces) → 20m Sled Pull (completo — tú lo haces) → 250m Remo → 30 Lunges → 500m Run</t>
         </is>
       </c>
       <c r="H527" s="82" t="n"/>
@@ -30966,9 +31177,12 @@
       <c r="D541" s="84" t="n"/>
       <c r="E541" s="84" t="n"/>
       <c r="F541" s="84" t="n"/>
-      <c r="G541" s="85" t="inlineStr">
-        <is>
-          <t>Foco: tecnica limpia, no maximo esfuerzo</t>
+      <c r="G541" s="235" t="inlineStr">
+        <is>
+          <t>Foco: tecnica limpia, no maximo esfuerzo
++ POTENCIA (al final, 10 min):
+3×6 Push Press (F18) — técnica fina
+Desc 60'' entre series</t>
         </is>
       </c>
       <c r="H541" s="84" t="n"/>
@@ -31290,9 +31504,11 @@
       <c r="D553" s="82" t="n"/>
       <c r="E553" s="82" t="n"/>
       <c r="F553" s="82" t="n"/>
-      <c r="G553" s="83" t="inlineStr">
-        <is>
-          <t>3-4 rondas: 10 Burpee Jump + 10 Wall Ball + 200m Remo</t>
+      <c r="G553" s="231" t="inlineStr">
+        <is>
+          <t>3-4 rondas: 8 Push Press (F18) + 10 Wall Ball + 200m Remo
+Desc 90'' entre rondas
+Push Press: peso técnico · Wall Ball: ritmo comp</t>
         </is>
       </c>
       <c r="H553" s="82" t="n"/>
@@ -31508,7 +31724,7 @@
       <c r="F563" s="82" t="n"/>
       <c r="G563" s="83" t="inlineStr">
         <is>
-          <t>500m Run → 500m Ski TOTAL (pareja, ~50% cada uno) → 500m Row TOTAL (pareja, ~50% cada uno)</t>
+          <t>500m Run → 250m Ski Erg → 250m Remo</t>
         </is>
       </c>
       <c r="H563" s="82" t="n"/>
@@ -31526,7 +31742,7 @@
       <c r="F564" s="82" t="n"/>
       <c r="G564" s="83" t="inlineStr">
         <is>
-          <t>→ 10m Sled Push (pareja: un atleta lo completa) → 10m Sled Pull (pareja: un atleta lo completa) → 10 WB TOTAL (pareja, ~50% cada uno) → 10 Lunges</t>
+          <t>→ 10m Sled Push (completo — tú lo haces) → 10m Sled Pull (completo — tú lo haces) → 5 Wall Balls → 10 Lunges</t>
         </is>
       </c>
       <c r="H564" s="82" t="n"/>
@@ -32048,7 +32264,7 @@
       <c r="F583" s="110" t="n"/>
       <c r="G583" s="137" t="inlineStr">
         <is>
-          <t>500m Run → 500m Ski TOTAL (pareja, ~50% cada uno) → 500m Row TOTAL (pareja, ~50% cada uno)</t>
+          <t>500m Run → 250m Ski Erg → 250m Remo</t>
         </is>
       </c>
       <c r="H583" s="110" t="n"/>
@@ -32066,7 +32282,7 @@
       <c r="F584" s="110" t="n"/>
       <c r="G584" s="137" t="inlineStr">
         <is>
-          <t>→ 10m Sled Push (pareja: un atleta lo completa) → 10m Sled Pull (pareja: un atleta lo completa) → 10 WB TOTAL (pareja, ~50% cada uno) → 10 Lunges</t>
+          <t>→ 10m Sled Push (completo — tú lo haces) → 10m Sled Pull (completo — tú lo haces) → 5 Wall Balls → 10 Lunges</t>
         </is>
       </c>
       <c r="H584" s="110" t="n"/>
@@ -32508,11 +32724,2880 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="220" t="inlineStr">
+        <is>
+          <t>Semana</t>
+        </is>
+      </c>
+      <c r="B1" s="220" t="inlineStr">
+        <is>
+          <t>Atleta</t>
+        </is>
+      </c>
+      <c r="C1" s="220" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="D1" s="220" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E1" s="220" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="F1" s="220" t="inlineStr">
+        <is>
+          <t>Notas sesión</t>
+        </is>
+      </c>
+      <c r="G1" s="220" t="inlineStr">
+        <is>
+          <t>Custom blocks (edits)</t>
+        </is>
+      </c>
+      <c r="H1" s="220" t="inlineStr">
+        <is>
+          <t>Extra blocks (añadidos)</t>
+        </is>
+      </c>
+      <c r="I1" s="220" t="inlineStr">
+        <is>
+          <t>Nota semanal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="221" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B2" s="221" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C2" s="221" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D2" s="221" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="E2" s="221" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="221" t="inlineStr">
+        <is>
+          <t>Press de banca con 20kg
+Dominadas no pude no tengo banda
+Hice superseries, sentadilla con plancha, press con rdl y hip thrust solo. Estuve 37 minutos. Los días de fuerza en gimnasio estan bien así, porque no tengo mucho tiempo. 45mina tops.
+Buenas sensaciones, la fatiga normal de hacer pesas</t>
+        </is>
+      </c>
+      <c r="G2" s="221" t="inlineStr"/>
+      <c r="H2" s="221" t="inlineStr"/>
+      <c r="I2" s="221" t="inlineStr">
+        <is>
+          <t>Mala  semana para comenzar, solo entrene un día, me dio fiebre, voy a entrar a la segunda semana sintiéndome muy gorda. Xabi no entreno nada. Segunda semana puede ser lo mismo que la primera, porque no hicimos nada, eso si4 días para mi de miercoles a sabado y 3 xabi de jueves a sabado</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="222" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B3" s="222" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C3" s="222" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="D3" s="222" t="inlineStr">
+        <is>
+          <t>no realizado</t>
+        </is>
+      </c>
+      <c r="E3" s="222" t="inlineStr"/>
+      <c r="F3" s="222" t="inlineStr"/>
+      <c r="G3" s="222" t="inlineStr"/>
+      <c r="H3" s="222" t="inlineStr"/>
+      <c r="I3" s="222" t="inlineStr">
+        <is>
+          <t>Mala  semana para comenzar, solo entrene un día, me dio fiebre, voy a entrar a la segunda semana sintiéndome muy gorda. Xabi no entreno nada. Segunda semana puede ser lo mismo que la primera, porque no hicimos nada, eso si4 días para mi de miercoles a sabado y 3 xabi de jueves a sabado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="222" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B4" s="222" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C4" s="222" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="D4" s="222" t="inlineStr">
+        <is>
+          <t>no realizado</t>
+        </is>
+      </c>
+      <c r="E4" s="222" t="inlineStr"/>
+      <c r="F4" s="222" t="inlineStr"/>
+      <c r="G4" s="222" t="inlineStr"/>
+      <c r="H4" s="222" t="inlineStr"/>
+      <c r="I4" s="222" t="inlineStr">
+        <is>
+          <t>Mala  semana para comenzar, solo entrene un día, me dio fiebre, voy a entrar a la segunda semana sintiéndome muy gorda. Xabi no entreno nada. Segunda semana puede ser lo mismo que la primera, porque no hicimos nada, eso si4 días para mi de miercoles a sabado y 3 xabi de jueves a sabado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="222" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B5" s="222" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C5" s="222" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="D5" s="222" t="inlineStr">
+        <is>
+          <t>no realizado</t>
+        </is>
+      </c>
+      <c r="E5" s="222" t="inlineStr"/>
+      <c r="F5" s="222" t="inlineStr"/>
+      <c r="G5" s="222" t="inlineStr"/>
+      <c r="H5" s="222" t="inlineStr"/>
+      <c r="I5" s="222" t="inlineStr">
+        <is>
+          <t>Mala  semana para comenzar, solo entrene un día, me dio fiebre, voy a entrar a la segunda semana sintiéndome muy gorda. Xabi no entreno nada. Segunda semana puede ser lo mismo que la primera, porque no hicimos nada, eso si4 días para mi de miercoles a sabado y 3 xabi de jueves a sabado</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="221" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B7" s="221" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C7" s="221" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="D7" s="221" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="E7" s="221" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="221" t="inlineStr">
+        <is>
+          <t>Muy tranquilo, 3 vueltas en todo, menos el trineo, no lo hicimos</t>
+        </is>
+      </c>
+      <c r="G7" s="221" t="inlineStr"/>
+      <c r="H7" s="221" t="inlineStr"/>
+      <c r="I7" s="221" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="221" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B8" s="221" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C8" s="221" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="D8" s="221" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="E8" s="221" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cansados pero es la primera vez así que muy bien. Vamos a ajustar a poner el tiempo de abajo por kilometro, no por cuanto hay que hacer la serie, eso te lo pongo yo luego. Por el hecho de la app que utilizamos calcula por km y luego va cortando los metros. 1x400m: 1:40’ 2x400: 1:54’ 3x400m: 2:06’ 4x400m: 2:28’ 5x400: 2:21’ 6x400: 2:15’ </t>
+        </is>
+      </c>
+      <c r="G8" s="221" t="inlineStr"/>
+      <c r="H8" s="221" t="inlineStr"/>
+      <c r="I8" s="221" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="221" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B9" s="221" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C9" s="221" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="D9" s="221" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="E9" s="221" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="221" t="inlineStr">
+        <is>
+          <t>Remo 1:55/500m y Ski 2:20/500m cansado y falta de aire, me queda mejorar la respiración mucho, wall ball muy cómodo con 5kg y con 7kg un poco mas duro pero en general bien, burpees terrible la técnica, queda depurar mucho pero salto lejos y tengo que aprovechar mi altura.</t>
+        </is>
+      </c>
+      <c r="G9" s="221" t="inlineStr"/>
+      <c r="H9" s="221" t="inlineStr"/>
+      <c r="I9" s="221" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="221" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B10" s="221" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C10" s="221" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="D10" s="221" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="E10" s="221" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="221" t="inlineStr">
+        <is>
+          <t>Con falta de aire, tengo que mejorar ek control de respiración. 1x400m: 1:26’ 2x400m: 1:37’ 3x400m: 2:06’ 4x400m: 2:08’ 5x400m: 2:12’ 6x400m: 2:17’</t>
+        </is>
+      </c>
+      <c r="G10" s="221" t="inlineStr"/>
+      <c r="H10" s="221" t="inlineStr"/>
+      <c r="I10" s="221" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="221" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B12" s="221" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C12" s="221" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D12" s="221" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="E12" s="221" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sentadilla con 40kg a 6reps. Trineo ambos ejercicios 100kg + peso trineo. </t>
+        </is>
+      </c>
+      <c r="G12" s="221" t="inlineStr"/>
+      <c r="H12" s="221" t="inlineStr"/>
+      <c r="I12" s="221" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="221" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B13" s="221" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C13" s="221" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="D13" s="221" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="E13" s="221" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hemos hecho en 25 min 4km. 1km a 6:09 2km a 6:05. 3km a 5:59. 4km a 6:38. </t>
+        </is>
+      </c>
+      <c r="G13" s="221" t="inlineStr"/>
+      <c r="H13" s="221" t="inlineStr"/>
+      <c r="I13" s="221" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="221" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B14" s="221" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C14" s="221" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="D14" s="221" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="E14" s="221" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="221" t="inlineStr">
+        <is>
+          <t>No hemos hecho los burpees porque el suelo quemaba. Agregamos sandbag son 20kg y hemos hecho 10. Farmer carries con 16kg por lado y fueron 25-30metros no estamos seguros. Y el ski y remo hemos hecho mas o menos de media 2:15 los 500metros Xabi y 2:30 mk. Mk comenzo bien pero a la 3 vuelta subio mucho. Fue al aire libre asi que el calor afecto mucho pero buenas sensaciones ambos</t>
+        </is>
+      </c>
+      <c r="G14" s="221" t="inlineStr">
+        <is>
+          <t>{
+ "4": {
+  "load": "Técnica",
+  "name": "Burpee Broad Jump",
+  "sets": "2x10"
+ }
+}</t>
+        </is>
+      </c>
+      <c r="H14" s="221" t="inlineStr">
+        <is>
+          <t>[
+ {
+  "load": "",
+  "name": "Lungee sandbag",
+  "sets": "3x10"
+ }
+]</t>
+        </is>
+      </c>
+      <c r="I14" s="221" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="221" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B15" s="221" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C15" s="221" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D15" s="221" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="E15" s="221" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="221" t="inlineStr"/>
+      <c r="G15" s="221" t="inlineStr"/>
+      <c r="H15" s="221" t="inlineStr"/>
+      <c r="I15" s="221" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="221" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B16" s="221" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C16" s="221" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="D16" s="221" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="E16" s="221" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="221" t="inlineStr"/>
+      <c r="G16" s="221" t="inlineStr"/>
+      <c r="H16" s="221" t="inlineStr"/>
+      <c r="I16" s="221" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="221" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B17" s="221" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C17" s="221" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="D17" s="221" t="inlineStr">
+        <is>
+          <t>COMPLETADO</t>
+        </is>
+      </c>
+      <c r="E17" s="221" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="221" t="inlineStr"/>
+      <c r="G17" s="221" t="inlineStr"/>
+      <c r="H17" s="221" t="inlineStr"/>
+      <c r="I17" s="221" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="220" t="inlineStr">
+        <is>
+          <t>Semana</t>
+        </is>
+      </c>
+      <c r="B1" s="220" t="inlineStr">
+        <is>
+          <t>Atleta</t>
+        </is>
+      </c>
+      <c r="C1" s="220" t="inlineStr">
+        <is>
+          <t>Versión</t>
+        </is>
+      </c>
+      <c r="D1" s="220" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="E1" s="220" t="inlineStr">
+        <is>
+          <t>Título</t>
+        </is>
+      </c>
+      <c r="F1" s="220" t="inlineStr">
+        <is>
+          <t>RPE obj</t>
+        </is>
+      </c>
+      <c r="G1" s="220" t="inlineStr">
+        <is>
+          <t>Ejercicio / Bloque</t>
+        </is>
+      </c>
+      <c r="H1" s="220" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="I1" s="220" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+      <c r="J1" s="220" t="inlineStr">
+        <is>
+          <t>Racional (cita fuente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="223" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B2" s="223" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C2" s="223" t="inlineStr">
+        <is>
+          <t>v6</t>
+        </is>
+      </c>
+      <c r="D2" s="223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="223" t="inlineStr">
+        <is>
+          <t>Nota semanal</t>
+        </is>
+      </c>
+      <c r="F2" s="223" t="inlineStr"/>
+      <c r="G2" s="223" t="inlineStr">
+        <is>
+          <t>MK completó 3/4 sesiones en S3. S3-D1: sentadilla 40kg (RPE 5, nota positiva aunque carga real fue ~73% RM — buena señal de fuerza). S3-D2: 4km en ~25min a ritmo Z2 correcto (6:05–6:38/km). S3-D3: HYROX afectado por calor exterior, sin burpees, Ski 2:30/500m en ronda 3 con subida de fatiga. S3-D4: no completada (patrón de incumplimiento Sábado en S2 y S3). Para S4: Sentadilla sube a 65% → 35kg (desde 32.5kg S3), Peso Muerto 65% → ~49kg (redondeado 47.5kg barra standard). Series de carrera reducidas a 3×1000m a ritmo conservador (5:30–5:50/km) en lugar de marcar tiempos agresivos. Se mantiene la estructura baseline de S4.</t>
+        </is>
+      </c>
+      <c r="H2" s="223" t="inlineStr"/>
+      <c r="I2" s="223" t="inlineStr"/>
+      <c r="J2" s="223" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="224" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B3" s="224" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C3" s="224" t="inlineStr">
+        <is>
+          <t>v6</t>
+        </is>
+      </c>
+      <c r="D3" s="224" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E3" s="224" t="inlineStr">
+        <is>
+          <t>Miércoles — Fuerza + Trineo (Primera Transferencia) · ~60'</t>
+        </is>
+      </c>
+      <c r="F3" s="224" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G3" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H3" s="224" t="inlineStr">
+        <is>
+          <t>1×5'</t>
+        </is>
+      </c>
+      <c r="I3" s="224" t="inlineStr">
+        <is>
+          <t>Assault Bike suave + movilidad dinámica (cadera, tobillo, hombro) + 2 rondas activación: Goblet Squat 5 reps + Hip Hinge 5 reps</t>
+        </is>
+      </c>
+      <c r="J3" s="224" t="inlineStr">
+        <is>
+          <t>Excel S4-MK-D1: Sentadilla 4×5 @65%→35kg + PM 4×4 @65%→50kg + Trineo Push+Pull 4×20m + Core 3×30''. Carga MK ajustada: 55kg RM × 0.65 = 35.75kg → 35kg (Batería F01). PM: MK sin RM registrado en Excel pero en S3-D1 reportó trineo+sentadilla 40kg con RPE 5, indicando capacidad — se usa 47.5kg como estimación conservadora al 65% del nivel funcional observado (Tema 5 §recuperación). Batería F01, F02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="224" t="inlineStr"/>
+      <c r="B4" s="224" t="inlineStr"/>
+      <c r="C4" s="224" t="inlineStr"/>
+      <c r="D4" s="224" t="inlineStr"/>
+      <c r="E4" s="224" t="inlineStr"/>
+      <c r="F4" s="224" t="inlineStr"/>
+      <c r="G4" s="224" t="inlineStr">
+        <is>
+          <t>Sentadilla (Back Squat)</t>
+        </is>
+      </c>
+      <c r="H4" s="224" t="inlineStr">
+        <is>
+          <t>4×5</t>
+        </is>
+      </c>
+      <c r="I4" s="224" t="inlineStr">
+        <is>
+          <t>35kg (65% RM 55kg). Bajar hasta paralelo, rodillas alineadas. Descanso 90''</t>
+        </is>
+      </c>
+      <c r="J4" s="224" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="224" t="inlineStr"/>
+      <c r="B5" s="224" t="inlineStr"/>
+      <c r="C5" s="224" t="inlineStr"/>
+      <c r="D5" s="224" t="inlineStr"/>
+      <c r="E5" s="224" t="inlineStr"/>
+      <c r="F5" s="224" t="inlineStr"/>
+      <c r="G5" s="224" t="inlineStr">
+        <is>
+          <t>Peso Muerto (Deadlift)</t>
+        </is>
+      </c>
+      <c r="H5" s="224" t="inlineStr">
+        <is>
+          <t>4×4</t>
+        </is>
+      </c>
+      <c r="I5" s="224" t="inlineStr">
+        <is>
+          <t>47.5kg (65% RM ~75kg estimado de PM — usar barra standard). Barra pegada al cuerpo. Descanso 90''</t>
+        </is>
+      </c>
+      <c r="J5" s="224" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="224" t="inlineStr"/>
+      <c r="B6" s="224" t="inlineStr"/>
+      <c r="C6" s="224" t="inlineStr"/>
+      <c r="D6" s="224" t="inlineStr"/>
+      <c r="E6" s="224" t="inlineStr"/>
+      <c r="F6" s="224" t="inlineStr"/>
+      <c r="G6" s="224" t="inlineStr">
+        <is>
+          <t>Sled Push (Trineo empuje)</t>
+        </is>
+      </c>
+      <c r="H6" s="224" t="inlineStr">
+        <is>
+          <t>4×20m</t>
+        </is>
+      </c>
+      <c r="I6" s="224" t="inlineStr">
+        <is>
+          <t>Carga ligera-media progresiva (técnica: pasos cortos, cuerpo ~45°). Individual — MK completa los 20m.</t>
+        </is>
+      </c>
+      <c r="J6" s="224" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="224" t="inlineStr"/>
+      <c r="B7" s="224" t="inlineStr"/>
+      <c r="C7" s="224" t="inlineStr"/>
+      <c r="D7" s="224" t="inlineStr"/>
+      <c r="E7" s="224" t="inlineStr"/>
+      <c r="F7" s="224" t="inlineStr"/>
+      <c r="G7" s="224" t="inlineStr">
+        <is>
+          <t>Sled Pull (Trineo arrastre)</t>
+        </is>
+      </c>
+      <c r="H7" s="224" t="inlineStr">
+        <is>
+          <t>4×20m</t>
+        </is>
+      </c>
+      <c r="I7" s="224" t="inlineStr">
+        <is>
+          <t>Carga ligera-media progresiva (caminar hacia atrás, cuerda tensa). Individual — MK completa los 20m.</t>
+        </is>
+      </c>
+      <c r="J7" s="224" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="224" t="inlineStr"/>
+      <c r="B8" s="224" t="inlineStr"/>
+      <c r="C8" s="224" t="inlineStr"/>
+      <c r="D8" s="224" t="inlineStr"/>
+      <c r="E8" s="224" t="inlineStr"/>
+      <c r="F8" s="224" t="inlineStr"/>
+      <c r="G8" s="224" t="inlineStr">
+        <is>
+          <t>Plancha (Plank)</t>
+        </is>
+      </c>
+      <c r="H8" s="224" t="inlineStr">
+        <is>
+          <t>3×30''</t>
+        </is>
+      </c>
+      <c r="I8" s="224" t="inlineStr">
+        <is>
+          <t>BW. Cadera neutra. Descanso 45'' entre series.</t>
+        </is>
+      </c>
+      <c r="J8" s="224" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="224" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B9" s="224" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C9" s="224" t="inlineStr">
+        <is>
+          <t>v6</t>
+        </is>
+      </c>
+      <c r="D9" s="224" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E9" s="224" t="inlineStr">
+        <is>
+          <t>Jueves — Carrera Z2 · ~55–65'</t>
+        </is>
+      </c>
+      <c r="F9" s="224" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H9" s="224" t="inlineStr">
+        <is>
+          <t>1×5'</t>
+        </is>
+      </c>
+      <c r="I9" s="224" t="inlineStr">
+        <is>
+          <t>Movilidad articular + 5' trote muy suave</t>
+        </is>
+      </c>
+      <c r="J9" s="224" t="inlineStr">
+        <is>
+          <t>Excel S4-MK-D2: Carrera continua 55–65 min + 6:00–6:30/km. S3-D2 completada con RPE 8 (objetivo era 6) lo que sugiere esfuerzo elevado — se mantiene la duración del baseline pero se recuerda explícitamente el ritmo inferior (6:00–6:30/km) para no repetir el patrón de fatiga. Tema 5 §recuperación (RPE real superior al planificado).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="224" t="inlineStr"/>
+      <c r="B10" s="224" t="inlineStr"/>
+      <c r="C10" s="224" t="inlineStr"/>
+      <c r="D10" s="224" t="inlineStr"/>
+      <c r="E10" s="224" t="inlineStr"/>
+      <c r="F10" s="224" t="inlineStr"/>
+      <c r="G10" s="224" t="inlineStr">
+        <is>
+          <t>Carrera Z2 continua</t>
+        </is>
+      </c>
+      <c r="H10" s="224" t="inlineStr">
+        <is>
+          <t>1×55–65 min</t>
+        </is>
+      </c>
+      <c r="I10" s="224" t="inlineStr">
+        <is>
+          <t>Ritmo: 6:00–6:30/km · FC &lt;75% FCmax · Ritmo conversacional. En S3-D2 MK completó 4km en ~25min a ritmo promedio 6:10/km con RPE 8 — se extiende la duración pero se mantiene el ritmo cómodo inferior sin forzar.</t>
+        </is>
+      </c>
+      <c r="J10" s="224" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="224" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B11" s="224" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C11" s="224" t="inlineStr">
+        <is>
+          <t>v6</t>
+        </is>
+      </c>
+      <c r="D11" s="224" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E11" s="224" t="inlineStr">
+        <is>
+          <t>Viernes — HYROX Específico (gym, pareja) · ~60'</t>
+        </is>
+      </c>
+      <c r="F11" s="224" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G11" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H11" s="224" t="inlineStr">
+        <is>
+          <t>1×8'</t>
+        </is>
+      </c>
+      <c r="I11" s="224" t="inlineStr">
+        <is>
+          <t>Ski Erg suave 3' + Remo suave 3' + movilidad hombro + 10 Wall Balls 6kg</t>
+        </is>
+      </c>
+      <c r="J11" s="224" t="inlineStr">
+        <is>
+          <t>Excel S4-MK-D3: 1 ronda fluida con 800m Run → 1000m Ski TOTAL → 20m Sled Push → 20m Sled Pull → 1000m Row TOTAL → 30 Lunges → 40 Burpees lentos → 50 WB TOTAL · WB 6kg. Sesión compartida con Xabi. MK usa 6kg WB (Rulebook §Doubles Mixed: WB 6kg). BBJ retomados en gym (en S3-D3 no se hicieron por calor exterior — patrón detectado, no es fallo físico sino logístico). Rulebook §estaciones: Sled Push/Pull = un atleta lo completa. Batería H01, H02, H03, H04, H05, H07, H08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="224" t="inlineStr"/>
+      <c r="B12" s="224" t="inlineStr"/>
+      <c r="C12" s="224" t="inlineStr"/>
+      <c r="D12" s="224" t="inlineStr"/>
+      <c r="E12" s="224" t="inlineStr"/>
+      <c r="F12" s="224" t="inlineStr"/>
+      <c r="G12" s="224" t="inlineStr">
+        <is>
+          <t>Run inicial</t>
+        </is>
+      </c>
+      <c r="H12" s="224" t="inlineStr">
+        <is>
+          <t>1×800m</t>
+        </is>
+      </c>
+      <c r="I12" s="224" t="inlineStr">
+        <is>
+          <t>Carrera a ~5:50–6:10/km. Individual.</t>
+        </is>
+      </c>
+      <c r="J12" s="224" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="224" t="inlineStr"/>
+      <c r="B13" s="224" t="inlineStr"/>
+      <c r="C13" s="224" t="inlineStr"/>
+      <c r="D13" s="224" t="inlineStr"/>
+      <c r="E13" s="224" t="inlineStr"/>
+      <c r="F13" s="224" t="inlineStr"/>
+      <c r="G13" s="224" t="inlineStr">
+        <is>
+          <t>Ski Erg</t>
+        </is>
+      </c>
+      <c r="H13" s="224" t="inlineStr">
+        <is>
+          <t>1×1000m TOTAL (pareja, ~500m cada uno)</t>
+        </is>
+      </c>
+      <c r="I13" s="224" t="inlineStr">
+        <is>
+          <t>MK: ~500m · Amortiguador 6 · Ritmo técnico, no máximo. (pareja: 1000m Ski TOTAL ~500m cada uno)</t>
+        </is>
+      </c>
+      <c r="J13" s="224" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="224" t="inlineStr"/>
+      <c r="B14" s="224" t="inlineStr"/>
+      <c r="C14" s="224" t="inlineStr"/>
+      <c r="D14" s="224" t="inlineStr"/>
+      <c r="E14" s="224" t="inlineStr"/>
+      <c r="F14" s="224" t="inlineStr"/>
+      <c r="G14" s="224" t="inlineStr">
+        <is>
+          <t>Sled Push (Trineo empuje)</t>
+        </is>
+      </c>
+      <c r="H14" s="224" t="inlineStr">
+        <is>
+          <t>1×20m</t>
+        </is>
+      </c>
+      <c r="I14" s="224" t="inlineStr">
+        <is>
+          <t>Carga ligera (primera vez en circuito completo) — un atleta lo completa antes del relevo (individual). (pareja: un atleta lo completa)</t>
+        </is>
+      </c>
+      <c r="J14" s="224" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="224" t="inlineStr"/>
+      <c r="B15" s="224" t="inlineStr"/>
+      <c r="C15" s="224" t="inlineStr"/>
+      <c r="D15" s="224" t="inlineStr"/>
+      <c r="E15" s="224" t="inlineStr"/>
+      <c r="F15" s="224" t="inlineStr"/>
+      <c r="G15" s="224" t="inlineStr">
+        <is>
+          <t>Sled Pull (Trineo arrastre)</t>
+        </is>
+      </c>
+      <c r="H15" s="224" t="inlineStr">
+        <is>
+          <t>1×20m</t>
+        </is>
+      </c>
+      <c r="I15" s="224" t="inlineStr">
+        <is>
+          <t>Carga ligera — un atleta lo completa antes del relevo (individual). (pareja: un atleta lo completa)</t>
+        </is>
+      </c>
+      <c r="J15" s="224" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="224" t="inlineStr"/>
+      <c r="B16" s="224" t="inlineStr"/>
+      <c r="C16" s="224" t="inlineStr"/>
+      <c r="D16" s="224" t="inlineStr"/>
+      <c r="E16" s="224" t="inlineStr"/>
+      <c r="F16" s="224" t="inlineStr"/>
+      <c r="G16" s="224" t="inlineStr">
+        <is>
+          <t>Remo (Rowing machine)</t>
+        </is>
+      </c>
+      <c r="H16" s="224" t="inlineStr">
+        <is>
+          <t>1×1000m TOTAL (pareja, ~500m cada uno)</t>
+        </is>
+      </c>
+      <c r="I16" s="224" t="inlineStr">
+        <is>
+          <t>MK: ~500m · Amortiguador 6 · Ritmo técnico. En S3-D3 MK hizo 2:30/500m en ronda 3 (fatiga) — objetivo aquí 2:20–2:30/500m constante. (pareja: 1000m Row TOTAL ~500m cada uno)</t>
+        </is>
+      </c>
+      <c r="J16" s="224" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="224" t="inlineStr"/>
+      <c r="B17" s="224" t="inlineStr"/>
+      <c r="C17" s="224" t="inlineStr"/>
+      <c r="D17" s="224" t="inlineStr"/>
+      <c r="E17" s="224" t="inlineStr"/>
+      <c r="F17" s="224" t="inlineStr"/>
+      <c r="G17" s="224" t="inlineStr">
+        <is>
+          <t>Lunges</t>
+        </is>
+      </c>
+      <c r="H17" s="224" t="inlineStr">
+        <is>
+          <t>1×30 reps</t>
+        </is>
+      </c>
+      <c r="I17" s="224" t="inlineStr">
+        <is>
+          <t>BW (sin carga esta semana — foco en técnica: rodilla trasera 1cm del suelo). Individual, alternando piernas.</t>
+        </is>
+      </c>
+      <c r="J17" s="224" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="224" t="inlineStr"/>
+      <c r="B18" s="224" t="inlineStr"/>
+      <c r="C18" s="224" t="inlineStr"/>
+      <c r="D18" s="224" t="inlineStr"/>
+      <c r="E18" s="224" t="inlineStr"/>
+      <c r="F18" s="224" t="inlineStr"/>
+      <c r="G18" s="224" t="inlineStr">
+        <is>
+          <t>Burpee Broad Jump (BBJ)</t>
+        </is>
+      </c>
+      <c r="H18" s="224" t="inlineStr">
+        <is>
+          <t>1×40 reps lentos</t>
+        </is>
+      </c>
+      <c r="I18" s="224" t="inlineStr">
+        <is>
+          <t>BW · Salto largo controlado. NOTA: en S3-D3 no se hicieron por calor exterior — esta sesión es en gym, se retoman con técnica limpia a ritmo bajo. (pareja: 40 BBJ TOTAL ~20 cada uno)</t>
+        </is>
+      </c>
+      <c r="J18" s="224" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="224" t="inlineStr"/>
+      <c r="B19" s="224" t="inlineStr"/>
+      <c r="C19" s="224" t="inlineStr"/>
+      <c r="D19" s="224" t="inlineStr"/>
+      <c r="E19" s="224" t="inlineStr"/>
+      <c r="F19" s="224" t="inlineStr"/>
+      <c r="G19" s="224" t="inlineStr">
+        <is>
+          <t>Wall Balls</t>
+        </is>
+      </c>
+      <c r="H19" s="224" t="inlineStr">
+        <is>
+          <t>1×50 reps TOTAL (pareja)</t>
+        </is>
+      </c>
+      <c r="I19" s="224" t="inlineStr">
+        <is>
+          <t>MK: 6kg · Diana 3m · En bloques de 10 con pausa entre bloques. (pareja: 50 WB TOTAL ~25 cada uno)</t>
+        </is>
+      </c>
+      <c r="J19" s="224" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="224" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B20" s="224" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C20" s="224" t="inlineStr">
+        <is>
+          <t>v6</t>
+        </is>
+      </c>
+      <c r="D20" s="224" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E20" s="224" t="inlineStr">
+        <is>
+          <t>Sábado — Series Carrera · ~55'</t>
+        </is>
+      </c>
+      <c r="F20" s="224" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G20" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H20" s="224" t="inlineStr">
+        <is>
+          <t>1×10'</t>
+        </is>
+      </c>
+      <c r="I20" s="224" t="inlineStr">
+        <is>
+          <t>Trote suave + técnica de carrera (elevación rodilla, zancada, frecuencia) + 3×100m progresivos</t>
+        </is>
+      </c>
+      <c r="J20" s="224" t="inlineStr">
+        <is>
+          <t>Excel S4-MK-D4: 3×1000m + Rec 2' + 5:10–5:30/km. Ritmo ajustado a 5:30–5:50/km por patrón de caída en series largas (S2-D4: tiempos 1:40→2:28/400m, caída clara; S3-D4 no completada — incumplimiento en D4 dos semanas consecutivas). Se reduce la exigencia de ritmo para garantizar adherencia y consistencia. Tema 5 §recuperación; macro_meso_micro §supercompensación (mejor completar con calidad que no completar por exceso de exigencia).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="224" t="inlineStr"/>
+      <c r="B21" s="224" t="inlineStr"/>
+      <c r="C21" s="224" t="inlineStr"/>
+      <c r="D21" s="224" t="inlineStr"/>
+      <c r="E21" s="224" t="inlineStr"/>
+      <c r="F21" s="224" t="inlineStr"/>
+      <c r="G21" s="224" t="inlineStr">
+        <is>
+          <t>Intervalos 1000m</t>
+        </is>
+      </c>
+      <c r="H21" s="224" t="inlineStr">
+        <is>
+          <t>3×1000m</t>
+        </is>
+      </c>
+      <c r="I21" s="224" t="inlineStr">
+        <is>
+          <t>Ritmo: 5:30–5:50/km (conservador vs Excel base 5:10–5:30/km). Recuperación: 2' caminando entre series. En S2-D4 MK arrancó a 4:10/km y cayó a 6:10/km en serie 4 — patrón de salida rápida. S3-D4 no completada. Objetivo: ritmo ESTABLE en las 3 series, no velocidad máxima.</t>
+        </is>
+      </c>
+      <c r="J21" s="224" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="224" t="inlineStr"/>
+      <c r="B22" s="224" t="inlineStr"/>
+      <c r="C22" s="224" t="inlineStr"/>
+      <c r="D22" s="224" t="inlineStr"/>
+      <c r="E22" s="224" t="inlineStr"/>
+      <c r="F22" s="224" t="inlineStr"/>
+      <c r="G22" s="224" t="inlineStr">
+        <is>
+          <t>Vuelta a la calma</t>
+        </is>
+      </c>
+      <c r="H22" s="224" t="inlineStr">
+        <is>
+          <t>1×5'</t>
+        </is>
+      </c>
+      <c r="I22" s="224" t="inlineStr">
+        <is>
+          <t>Trote suave + estiramientos estáticos</t>
+        </is>
+      </c>
+      <c r="J22" s="224" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="223" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B23" s="223" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C23" s="223" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D23" s="223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="223" t="inlineStr">
+        <is>
+          <t>Nota semanal</t>
+        </is>
+      </c>
+      <c r="F23" s="223" t="inlineStr"/>
+      <c r="G23" s="223" t="inlineStr">
+        <is>
+          <t>Xabi completó 3/4 sesiones en S3. S3-D1: RPE 3 (muy bajo, carga de fuerza muy accesible — confirma que 65% RM es subestímulo para Xabi en fuerza). S3-D2: RPE 8 (Z2 resultó exigente — patrón similar a MK, ritmo Z2 a controlar). S3-D3: RPE 7, calor exterior afectó (sin burpees, Ski 2:15/500m constante — mejor que MK). S3-D4: no completada (patrón incumplimiento D4 en S2 y S3). Para S4: Sentadilla sube a 65% → 40kg (desde 35kg S3), PM 65% → 52.5kg. En D1 la carga sigue siendo manejable (RPE 3 en S3-D1 sugiere hay margen). Series de carrera: 3×1000m a ritmo estable conservador dado patrón de no completar D4. Respiración sigue siendo punto de trabajo en Ski/Row y BBJ.</t>
+        </is>
+      </c>
+      <c r="H23" s="223" t="inlineStr"/>
+      <c r="I23" s="223" t="inlineStr"/>
+      <c r="J23" s="223" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="224" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B24" s="224" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C24" s="224" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D24" s="224" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E24" s="224" t="inlineStr">
+        <is>
+          <t>Miércoles — Fuerza + Trineo (Primera Transferencia) · ~60'</t>
+        </is>
+      </c>
+      <c r="F24" s="224" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G24" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H24" s="224" t="inlineStr">
+        <is>
+          <t>1×5'</t>
+        </is>
+      </c>
+      <c r="I24" s="224" t="inlineStr">
+        <is>
+          <t>Assault Bike suave + movilidad dinámica (cadera, tobillo, hombro) + 2 rondas activación: Goblet Squat 5 reps + Hip Hinge 5 reps</t>
+        </is>
+      </c>
+      <c r="J24" s="224" t="inlineStr">
+        <is>
+          <t>Excel S4-Xabi-D1: Sentadilla 4×5 @65%→40kg + PM 4×4 @65%→52.5kg + Trineo Push+Pull 4×20m + Core 3×30''. Cargas coinciden exactamente con el baseline del Excel. En S3-D1 Xabi reportó RPE 3 — no se reduce porque el RPE bajo indica que la fase introductoria era subestímulo; S4 al 65% es la progresión correcta según el plan maestro. Batería F01, F02, H03, H04, R01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="224" t="inlineStr"/>
+      <c r="B25" s="224" t="inlineStr"/>
+      <c r="C25" s="224" t="inlineStr"/>
+      <c r="D25" s="224" t="inlineStr"/>
+      <c r="E25" s="224" t="inlineStr"/>
+      <c r="F25" s="224" t="inlineStr"/>
+      <c r="G25" s="224" t="inlineStr">
+        <is>
+          <t>Sentadilla (Back Squat)</t>
+        </is>
+      </c>
+      <c r="H25" s="224" t="inlineStr">
+        <is>
+          <t>4×5</t>
+        </is>
+      </c>
+      <c r="I25" s="224" t="inlineStr">
+        <is>
+          <t>40kg (65% RM 60kg → 39kg, redondeado 40kg). Bajar hasta paralelo, rodillas alineadas. Descanso 90''. NOTA: en S3-D1 Xabi realizó sentadilla con RPE 3 a carga similar — se confirma la progresión a 65% sin reducción. (Batería F01)</t>
+        </is>
+      </c>
+      <c r="J25" s="224" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="224" t="inlineStr"/>
+      <c r="B26" s="224" t="inlineStr"/>
+      <c r="C26" s="224" t="inlineStr"/>
+      <c r="D26" s="224" t="inlineStr"/>
+      <c r="E26" s="224" t="inlineStr"/>
+      <c r="F26" s="224" t="inlineStr"/>
+      <c r="G26" s="224" t="inlineStr">
+        <is>
+          <t>Peso Muerto (Deadlift)</t>
+        </is>
+      </c>
+      <c r="H26" s="224" t="inlineStr">
+        <is>
+          <t>4×4</t>
+        </is>
+      </c>
+      <c r="I26" s="224" t="inlineStr">
+        <is>
+          <t>52.5kg (65% RM 80kg → 52kg, redondeado 52.5kg). Barra pegada al cuerpo, cadera empuja al subir. Descanso 90''. (Batería F02)</t>
+        </is>
+      </c>
+      <c r="J26" s="224" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="224" t="inlineStr"/>
+      <c r="B27" s="224" t="inlineStr"/>
+      <c r="C27" s="224" t="inlineStr"/>
+      <c r="D27" s="224" t="inlineStr"/>
+      <c r="E27" s="224" t="inlineStr"/>
+      <c r="F27" s="224" t="inlineStr"/>
+      <c r="G27" s="224" t="inlineStr">
+        <is>
+          <t>Sled Push (Trineo empuje)</t>
+        </is>
+      </c>
+      <c r="H27" s="224" t="inlineStr">
+        <is>
+          <t>4×20m</t>
+        </is>
+      </c>
+      <c r="I27" s="224" t="inlineStr">
+        <is>
+          <t>Carga progresiva (técnica: pasos cortos, cuerpo ~45°). Individual — Xabi completa los 20m.</t>
+        </is>
+      </c>
+      <c r="J27" s="224" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="224" t="inlineStr"/>
+      <c r="B28" s="224" t="inlineStr"/>
+      <c r="C28" s="224" t="inlineStr"/>
+      <c r="D28" s="224" t="inlineStr"/>
+      <c r="E28" s="224" t="inlineStr"/>
+      <c r="F28" s="224" t="inlineStr"/>
+      <c r="G28" s="224" t="inlineStr">
+        <is>
+          <t>Sled Pull (Trineo arrastre)</t>
+        </is>
+      </c>
+      <c r="H28" s="224" t="inlineStr">
+        <is>
+          <t>4×20m</t>
+        </is>
+      </c>
+      <c r="I28" s="224" t="inlineStr">
+        <is>
+          <t>Carga progresiva (caminar hacia atrás, cuerda tensa). Individual — Xabi completa los 20m.</t>
+        </is>
+      </c>
+      <c r="J28" s="224" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="224" t="inlineStr"/>
+      <c r="B29" s="224" t="inlineStr"/>
+      <c r="C29" s="224" t="inlineStr"/>
+      <c r="D29" s="224" t="inlineStr"/>
+      <c r="E29" s="224" t="inlineStr"/>
+      <c r="F29" s="224" t="inlineStr"/>
+      <c r="G29" s="224" t="inlineStr">
+        <is>
+          <t>Plancha (Plank)</t>
+        </is>
+      </c>
+      <c r="H29" s="224" t="inlineStr">
+        <is>
+          <t>3×30''</t>
+        </is>
+      </c>
+      <c r="I29" s="224" t="inlineStr">
+        <is>
+          <t>BW. Cadera neutra. Descanso 45'' entre series.</t>
+        </is>
+      </c>
+      <c r="J29" s="224" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="224" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B30" s="224" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C30" s="224" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D30" s="224" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E30" s="224" t="inlineStr">
+        <is>
+          <t>Jueves — Carrera Z2 · ~55–65'</t>
+        </is>
+      </c>
+      <c r="F30" s="224" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G30" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H30" s="224" t="inlineStr">
+        <is>
+          <t>1×5'</t>
+        </is>
+      </c>
+      <c r="I30" s="224" t="inlineStr">
+        <is>
+          <t>Movilidad articular + 5' trote muy suave</t>
+        </is>
+      </c>
+      <c r="J30" s="224" t="inlineStr">
+        <is>
+          <t>Excel S4-Xabi-D2: Carrera continua 55–65 min + cómodo. S3-D2 completada con RPE 8 (objetivo era 6) — patrón de esfuerzo excesivo en Z2. Se mantiene duración baseline pero se insiste en ritmo conversacional real. Tema 5 §recuperación (RPE real superior al planificado indica acumulación de fatiga si se repite).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="224" t="inlineStr"/>
+      <c r="B31" s="224" t="inlineStr"/>
+      <c r="C31" s="224" t="inlineStr"/>
+      <c r="D31" s="224" t="inlineStr"/>
+      <c r="E31" s="224" t="inlineStr"/>
+      <c r="F31" s="224" t="inlineStr"/>
+      <c r="G31" s="224" t="inlineStr">
+        <is>
+          <t>Carrera Z2 continua</t>
+        </is>
+      </c>
+      <c r="H31" s="224" t="inlineStr">
+        <is>
+          <t>1×55–65 min</t>
+        </is>
+      </c>
+      <c r="I31" s="224" t="inlineStr">
+        <is>
+          <t>Ritmo: cómodo, conversacional · FC &lt;75% FCmax. Xabi reportó RPE 8 en S3-D2 para Z2 — recordatorio de mantener ritmo VERDADERAMENTE cómodo, sin competir con MK. Aproximado: 6:00–6:40/km según sensaciones.</t>
+        </is>
+      </c>
+      <c r="J31" s="224" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="224" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B32" s="224" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C32" s="224" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D32" s="224" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E32" s="224" t="inlineStr">
+        <is>
+          <t>Viernes — HYROX Específico (gym, pareja) · ~60'</t>
+        </is>
+      </c>
+      <c r="F32" s="224" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G32" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H32" s="224" t="inlineStr">
+        <is>
+          <t>1×8'</t>
+        </is>
+      </c>
+      <c r="I32" s="224" t="inlineStr">
+        <is>
+          <t>Ski Erg suave 3' + Remo suave 3' + movilidad hombro + 10 Wall Balls 6kg (Xabi puede usar 7–9kg en calentamiento para referencia)</t>
+        </is>
+      </c>
+      <c r="J32" s="224" t="inlineStr">
+        <is>
+          <t>Excel S4-Xabi-D3: 1 ronda fluida: 800m Run → 1000m Ski TOTAL → 20m Sled Push → 20m Sled Pull → 1000m Row TOTAL → 30 Lunges → 40 Burpees lentos → 50 WB TOTAL · WB 6–9kg. Sesión compartida con MK. Xabi usa 6–9kg WB (Batería H08: Xabi ref 6–9kg; Rulebook §Doubles Mixed WB 6kg en competición pero en entrenamiento técnico puede usarse 9kg). BBJ con foco en técnica (patrón S2-D3: técnica a depurar). Rulebook §estaciones: Sled Push/Pull = un atleta lo completa. Batería H01, H02, H03, H04, H05, H07, H08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="224" t="inlineStr"/>
+      <c r="B33" s="224" t="inlineStr"/>
+      <c r="C33" s="224" t="inlineStr"/>
+      <c r="D33" s="224" t="inlineStr"/>
+      <c r="E33" s="224" t="inlineStr"/>
+      <c r="F33" s="224" t="inlineStr"/>
+      <c r="G33" s="224" t="inlineStr">
+        <is>
+          <t>Run inicial</t>
+        </is>
+      </c>
+      <c r="H33" s="224" t="inlineStr">
+        <is>
+          <t>1×800m</t>
+        </is>
+      </c>
+      <c r="I33" s="224" t="inlineStr">
+        <is>
+          <t>Carrera a ritmo cómodo ~5:30–6:00/km. Individual.</t>
+        </is>
+      </c>
+      <c r="J33" s="224" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="224" t="inlineStr"/>
+      <c r="B34" s="224" t="inlineStr"/>
+      <c r="C34" s="224" t="inlineStr"/>
+      <c r="D34" s="224" t="inlineStr"/>
+      <c r="E34" s="224" t="inlineStr"/>
+      <c r="F34" s="224" t="inlineStr"/>
+      <c r="G34" s="224" t="inlineStr">
+        <is>
+          <t>Ski Erg</t>
+        </is>
+      </c>
+      <c r="H34" s="224" t="inlineStr">
+        <is>
+          <t>1×1000m TOTAL (pareja, ~500m cada uno)</t>
+        </is>
+      </c>
+      <c r="I34" s="224" t="inlineStr">
+        <is>
+          <t>Xabi: ~500m · Amortiguador 6 · En S3-D3 Xabi mantuvo 2:15/500m constante — objetivo mantener ese ritmo. FOCO: respiración rítmica (patrón detectado S2-D3: falta de aire). (pareja: 1000m Ski TOTAL ~500m cada uno)</t>
+        </is>
+      </c>
+      <c r="J34" s="224" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="224" t="inlineStr"/>
+      <c r="B35" s="224" t="inlineStr"/>
+      <c r="C35" s="224" t="inlineStr"/>
+      <c r="D35" s="224" t="inlineStr"/>
+      <c r="E35" s="224" t="inlineStr"/>
+      <c r="F35" s="224" t="inlineStr"/>
+      <c r="G35" s="224" t="inlineStr">
+        <is>
+          <t>Sled Push (Trineo empuje)</t>
+        </is>
+      </c>
+      <c r="H35" s="224" t="inlineStr">
+        <is>
+          <t>1×20m</t>
+        </is>
+      </c>
+      <c r="I35" s="224" t="inlineStr">
+        <is>
+          <t>Carga ligera — un atleta lo completa antes del relevo (individual). (pareja: un atleta lo completa)</t>
+        </is>
+      </c>
+      <c r="J35" s="224" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="224" t="inlineStr"/>
+      <c r="B36" s="224" t="inlineStr"/>
+      <c r="C36" s="224" t="inlineStr"/>
+      <c r="D36" s="224" t="inlineStr"/>
+      <c r="E36" s="224" t="inlineStr"/>
+      <c r="F36" s="224" t="inlineStr"/>
+      <c r="G36" s="224" t="inlineStr">
+        <is>
+          <t>Sled Pull (Trineo arrastre)</t>
+        </is>
+      </c>
+      <c r="H36" s="224" t="inlineStr">
+        <is>
+          <t>1×20m</t>
+        </is>
+      </c>
+      <c r="I36" s="224" t="inlineStr">
+        <is>
+          <t>Carga ligera — un atleta lo completa antes del relevo (individual). (pareja: un atleta lo completa)</t>
+        </is>
+      </c>
+      <c r="J36" s="224" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="224" t="inlineStr"/>
+      <c r="B37" s="224" t="inlineStr"/>
+      <c r="C37" s="224" t="inlineStr"/>
+      <c r="D37" s="224" t="inlineStr"/>
+      <c r="E37" s="224" t="inlineStr"/>
+      <c r="F37" s="224" t="inlineStr"/>
+      <c r="G37" s="224" t="inlineStr">
+        <is>
+          <t>Remo (Rowing machine)</t>
+        </is>
+      </c>
+      <c r="H37" s="224" t="inlineStr">
+        <is>
+          <t>1×1000m TOTAL (pareja, ~500m cada uno)</t>
+        </is>
+      </c>
+      <c r="I37" s="224" t="inlineStr">
+        <is>
+          <t>Xabi: ~500m · Amortiguador 6 · En S2-D3 Xabi hizo 1:55/500m — referencia de capacidad. Ritmo técnico sin máximo esfuerzo. (pareja: 1000m Row TOTAL ~500m cada uno)</t>
+        </is>
+      </c>
+      <c r="J37" s="224" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="224" t="inlineStr"/>
+      <c r="B38" s="224" t="inlineStr"/>
+      <c r="C38" s="224" t="inlineStr"/>
+      <c r="D38" s="224" t="inlineStr"/>
+      <c r="E38" s="224" t="inlineStr"/>
+      <c r="F38" s="224" t="inlineStr"/>
+      <c r="G38" s="224" t="inlineStr">
+        <is>
+          <t>Lunges</t>
+        </is>
+      </c>
+      <c r="H38" s="224" t="inlineStr">
+        <is>
+          <t>1×30 reps</t>
+        </is>
+      </c>
+      <c r="I38" s="224" t="inlineStr">
+        <is>
+          <t>BW (sin carga — foco técnico: rodilla trasera 1cm del suelo, paso controlado). Individual.</t>
+        </is>
+      </c>
+      <c r="J38" s="224" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="224" t="inlineStr"/>
+      <c r="B39" s="224" t="inlineStr"/>
+      <c r="C39" s="224" t="inlineStr"/>
+      <c r="D39" s="224" t="inlineStr"/>
+      <c r="E39" s="224" t="inlineStr"/>
+      <c r="F39" s="224" t="inlineStr"/>
+      <c r="G39" s="224" t="inlineStr">
+        <is>
+          <t>Burpee Broad Jump (BBJ)</t>
+        </is>
+      </c>
+      <c r="H39" s="224" t="inlineStr">
+        <is>
+          <t>1×40 reps lentos</t>
+        </is>
+      </c>
+      <c r="I39" s="224" t="inlineStr">
+        <is>
+          <t>BW · FOCO TÉCNICO: en S2-D3 Xabi identificó que tiene técnica a depurar y aprovecha altura. Sesión en gym (sin calor exterior) — ritmo lento, salto largo aprovechando la altura. (pareja: 40 BBJ TOTAL ~20 cada uno)</t>
+        </is>
+      </c>
+      <c r="J39" s="224" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="224" t="inlineStr"/>
+      <c r="B40" s="224" t="inlineStr"/>
+      <c r="C40" s="224" t="inlineStr"/>
+      <c r="D40" s="224" t="inlineStr"/>
+      <c r="E40" s="224" t="inlineStr"/>
+      <c r="F40" s="224" t="inlineStr"/>
+      <c r="G40" s="224" t="inlineStr">
+        <is>
+          <t>Wall Balls</t>
+        </is>
+      </c>
+      <c r="H40" s="224" t="inlineStr">
+        <is>
+          <t>1×50 reps TOTAL (pareja)</t>
+        </is>
+      </c>
+      <c r="I40" s="224" t="inlineStr">
+        <is>
+          <t>Xabi: 6–9kg (en S2-D3 fue cómodo con 5kg y 7kg) · Diana 3m · En bloques de 10. (pareja: 50 WB TOTAL ~25 cada uno)</t>
+        </is>
+      </c>
+      <c r="J40" s="224" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="224" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B41" s="224" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C41" s="224" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="D41" s="224" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E41" s="224" t="inlineStr">
+        <is>
+          <t>Sábado — Series Carrera · ~55'</t>
+        </is>
+      </c>
+      <c r="F41" s="224" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G41" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H41" s="224" t="inlineStr">
+        <is>
+          <t>1×10'</t>
+        </is>
+      </c>
+      <c r="I41" s="224" t="inlineStr">
+        <is>
+          <t>Trote suave + técnica de carrera (elevación rodilla, zancada, frecuencia) + 3×100m progresivos</t>
+        </is>
+      </c>
+      <c r="J41" s="224" t="inlineStr">
+        <is>
+          <t>Excel S4-Xabi-D4: 3×1000m + Rec 2' + a su ritmo progresando. Ritmo orientativo 5:15–5:35/km basado en tiempos S2-D4 (capacidad demostrada 5:15/km pero con caída) y foco en estabilidad (patrón: salida demasiado rápida en S2-D4 — nota del Excel: 'arrancar a 5:30–5:45/km y mantener'). S3-D4 no completada — incumplimiento en D4 dos semanas consecutivas sugiere que la sesión del sábado es la más difícil de adherir; se mantiene el volumen reducido (3×1000m) para facilitar adherencia. Tema 5 §recuperación; macro_meso_micro §supercompensación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="224" t="inlineStr"/>
+      <c r="B42" s="224" t="inlineStr"/>
+      <c r="C42" s="224" t="inlineStr"/>
+      <c r="D42" s="224" t="inlineStr"/>
+      <c r="E42" s="224" t="inlineStr"/>
+      <c r="F42" s="224" t="inlineStr"/>
+      <c r="G42" s="224" t="inlineStr">
+        <is>
+          <t>Intervalos 1000m</t>
+        </is>
+      </c>
+      <c r="H42" s="224" t="inlineStr">
+        <is>
+          <t>3×1000m</t>
+        </is>
+      </c>
+      <c r="I42" s="224" t="inlineStr">
+        <is>
+          <t>Ritmo: 5:15–5:35/km estable (Xabi tiene mayor capacidad de carrera que MK — en S2-D4 arrancó a 3:35/km y bajó a 5:42/km; objetivo es ESTABILIDAD no velocidad). Recuperación: 2' caminando. CLAVE: arrancar a 5:35/km y NO más rápido — patrón de salida explosiva detectado en S2-D4.</t>
+        </is>
+      </c>
+      <c r="J42" s="224" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="224" t="inlineStr"/>
+      <c r="B43" s="224" t="inlineStr"/>
+      <c r="C43" s="224" t="inlineStr"/>
+      <c r="D43" s="224" t="inlineStr"/>
+      <c r="E43" s="224" t="inlineStr"/>
+      <c r="F43" s="224" t="inlineStr"/>
+      <c r="G43" s="224" t="inlineStr">
+        <is>
+          <t>Vuelta a la calma</t>
+        </is>
+      </c>
+      <c r="H43" s="224" t="inlineStr">
+        <is>
+          <t>1×5'</t>
+        </is>
+      </c>
+      <c r="I43" s="224" t="inlineStr">
+        <is>
+          <t>Trote suave + estiramientos estáticos + trabajo de respiración</t>
+        </is>
+      </c>
+      <c r="J43" s="224" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="223" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B45" s="223" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C45" s="223" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="D45" s="223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="223" t="inlineStr">
+        <is>
+          <t>Nota semanal</t>
+        </is>
+      </c>
+      <c r="F45" s="223" t="inlineStr"/>
+      <c r="G45" s="223" t="inlineStr">
+        <is>
+          <t>S5 Base Aerobica · 4 dias · RPE objetivo 7-8 · 65-70% RM · 'Subir umbral'. ANALISIS REGISTROS COMPLETO MK: S1 solo D1 fuerza completada (fiebre el resto, RPE 5 a 30kg sentadilla). S2-D3 HYROX RPE 5 (sin trineo). S2-D4 series RPE 8 (alto sostenido). S3-D1 fuerza RPE 5 con sentadilla 40kg + trineo 100kg+ (bien tolerada, en objetivo). S3-D2 Z2 RPE 8 (objetivo 6, +2 puntos) con caida pronunciada en km4 (6:09 -&gt; 6:38). S3-D3 HYROX RPE 7 sin burpees por calor exterior. AJUSTES S5: mantener carga fuerza baseline Excel S5 (sentadilla 37.5kg, PM 55kg — coherente con tolerancia mostrada en S3-D1); ritmo</t>
+        </is>
+      </c>
+      <c r="H45" s="223" t="inlineStr"/>
+      <c r="I45" s="223" t="inlineStr"/>
+      <c r="J45" s="223" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="224" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B46" s="224" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C46" s="224" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="D46" s="224" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E46" s="224" t="inlineStr">
+        <is>
+          <t>Miercoles — Fuerza + Trineo · ~60' · Subir umbral</t>
+        </is>
+      </c>
+      <c r="F46" s="224" t="inlineStr">
+        <is>
+          <t>RPE 7-8</t>
+        </is>
+      </c>
+      <c r="G46" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H46" s="224" t="inlineStr">
+        <is>
+          <t>1x5'</t>
+        </is>
+      </c>
+      <c r="I46" s="224" t="inlineStr">
+        <is>
+          <t>5' Assault Bike + movilidad dinamica caderas/tobillos + 2r activacion (goblet squat + hip hinge)</t>
+        </is>
+      </c>
+      <c r="J46" s="224" t="inlineStr">
+        <is>
+          <t>Baseline literal Excel S5-MK-D1 (Sentadilla 4x5 @70%-&gt;37.5kg, PM 4x4 @75%-&gt;55kg, Trineo 4x20m, Core 3x30''). S3-D1 MK toleró sentadilla 40kg con RPE 5; el incremento Excel a 37.5kg @70% (vs @60% en S3) es la progresion natural del plan. Mantener trineo en carga media — S3-D1 con 100kg+ fue RPE 5 (cita Bateria §H03 Sled Push, tecnica: pasos cortos, cuerpo ~45°).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="224" t="inlineStr"/>
+      <c r="B47" s="224" t="inlineStr"/>
+      <c r="C47" s="224" t="inlineStr"/>
+      <c r="D47" s="224" t="inlineStr"/>
+      <c r="E47" s="224" t="inlineStr"/>
+      <c r="F47" s="224" t="inlineStr"/>
+      <c r="G47" s="224" t="inlineStr">
+        <is>
+          <t>Sentadilla (Bateria F01)</t>
+        </is>
+      </c>
+      <c r="H47" s="224" t="inlineStr">
+        <is>
+          <t>4x5</t>
+        </is>
+      </c>
+      <c r="I47" s="224" t="inlineStr">
+        <is>
+          <t>@70% RM -&gt; 37.5kg · Desc 60–90'' entre series</t>
+        </is>
+      </c>
+      <c r="J47" s="224" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="224" t="inlineStr"/>
+      <c r="B48" s="224" t="inlineStr"/>
+      <c r="C48" s="224" t="inlineStr"/>
+      <c r="D48" s="224" t="inlineStr"/>
+      <c r="E48" s="224" t="inlineStr"/>
+      <c r="F48" s="224" t="inlineStr"/>
+      <c r="G48" s="224" t="inlineStr">
+        <is>
+          <t>Peso Muerto (Bateria F02)</t>
+        </is>
+      </c>
+      <c r="H48" s="224" t="inlineStr">
+        <is>
+          <t>4x4</t>
+        </is>
+      </c>
+      <c r="I48" s="224" t="inlineStr">
+        <is>
+          <t>@75% RM -&gt; 55kg · Desc 60–90'' entre series</t>
+        </is>
+      </c>
+      <c r="J48" s="224" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="224" t="inlineStr"/>
+      <c r="B49" s="224" t="inlineStr"/>
+      <c r="C49" s="224" t="inlineStr"/>
+      <c r="D49" s="224" t="inlineStr"/>
+      <c r="E49" s="224" t="inlineStr"/>
+      <c r="F49" s="224" t="inlineStr"/>
+      <c r="G49" s="224" t="inlineStr">
+        <is>
+          <t>Trineo Push + Pull (Bateria H03/H04)</t>
+        </is>
+      </c>
+      <c r="H49" s="224" t="inlineStr">
+        <is>
+          <t>4x20m Push + 4x20m Pull</t>
+        </is>
+      </c>
+      <c r="I49" s="224" t="inlineStr">
+        <is>
+          <t>Carga media (similar a S3-D1 con 100kg+peso trineo bien tolerado) · Desc 60–90'' entre pasadas</t>
+        </is>
+      </c>
+      <c r="J49" s="224" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="224" t="inlineStr"/>
+      <c r="B50" s="224" t="inlineStr"/>
+      <c r="C50" s="224" t="inlineStr"/>
+      <c r="D50" s="224" t="inlineStr"/>
+      <c r="E50" s="224" t="inlineStr"/>
+      <c r="F50" s="224" t="inlineStr"/>
+      <c r="G50" s="224" t="inlineStr">
+        <is>
+          <t>Core — Plancha (Bateria R01)</t>
+        </is>
+      </c>
+      <c r="H50" s="224" t="inlineStr">
+        <is>
+          <t>3x30''</t>
+        </is>
+      </c>
+      <c r="I50" s="224" t="inlineStr">
+        <is>
+          <t>BW · Desc 45''</t>
+        </is>
+      </c>
+      <c r="J50" s="224" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="224" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B51" s="224" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C51" s="224" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="D51" s="224" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E51" s="224" t="inlineStr">
+        <is>
+          <t>Jueves — Carrera Z2 conservadora · ~55-60'</t>
+        </is>
+      </c>
+      <c r="F51" s="224" t="inlineStr">
+        <is>
+          <t>RPE 6</t>
+        </is>
+      </c>
+      <c r="G51" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H51" s="224" t="inlineStr">
+        <is>
+          <t>1x10'</t>
+        </is>
+      </c>
+      <c r="I51" s="224" t="inlineStr">
+        <is>
+          <t>5' movilidad + 5' trote muy suave</t>
+        </is>
+      </c>
+      <c r="J51" s="224" t="inlineStr">
+        <is>
+          <t>Baseline Excel S5-MK-D2 (55–65 min @ 6:00–6:30/km). AJUSTE: ritmo conservado 6:20–6:40/km basado en S3-D2 RPE real = 8 vs objetivo 6 (+2 puntos), con caida sostenida en km4 (1:40 -&gt; 2:28/400m equivalente 6:09 -&gt; 6:38/km). Cita macro_meso_micro §carga progresiva — reducir intensidad mantiene volumen aerobico sin sobreestimular. Tema 6 §interferencia AMPK/mTOR: tras fuerza del miercoles, bajar carga del cardio del jueves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="224" t="inlineStr"/>
+      <c r="B52" s="224" t="inlineStr"/>
+      <c r="C52" s="224" t="inlineStr"/>
+      <c r="D52" s="224" t="inlineStr"/>
+      <c r="E52" s="224" t="inlineStr"/>
+      <c r="F52" s="224" t="inlineStr"/>
+      <c r="G52" s="224" t="inlineStr">
+        <is>
+          <t>Carrera continua Z2 (Bateria C01)</t>
+        </is>
+      </c>
+      <c r="H52" s="224" t="inlineStr">
+        <is>
+          <t>1x55 min</t>
+        </is>
+      </c>
+      <c r="I52" s="224" t="inlineStr">
+        <is>
+          <t>Ritmo 6:20–6:40/km · FC &lt;75% FCmax · MK ritmo conservador, hablar sin problema. Si sensaciones buenas en min 40, mantener; si fatiga acumulada cortar a 50 min.</t>
+        </is>
+      </c>
+      <c r="J52" s="224" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="224" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B53" s="224" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C53" s="224" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="D53" s="224" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E53" s="224" t="inlineStr">
+        <is>
+          <t>Viernes — HYROX Especifico (pareja) · ~60'</t>
+        </is>
+      </c>
+      <c r="F53" s="224" t="inlineStr">
+        <is>
+          <t>RPE 7</t>
+        </is>
+      </c>
+      <c r="G53" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H53" s="224" t="inlineStr">
+        <is>
+          <t>1x8'</t>
+        </is>
+      </c>
+      <c r="I53" s="224" t="inlineStr">
+        <is>
+          <t>8' Ski o Remo suave amortiguador 5 + movilidad hombro + 10 Wall Balls 6kg activacion</t>
+        </is>
+      </c>
+      <c r="J53" s="224" t="inlineStr">
+        <is>
+          <t>Baseline Excel S5-MK-D3 (3 rondas HYROX, juntos). Distancias TOTAL pareja segun Rulebook Doubles §6: Ski/Row/WB se reparten libremente entre los 2 atletas (~50% cada uno); Sled Push, Sled Pull, Sandbag Lunges = un solo atleta lo completa antes del relevo. S3-D3 RPE 7 fue OK pero sin burpees por calor — incluirlos esta vez con calor controlado (mañana o noche).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="224" t="inlineStr"/>
+      <c r="B54" s="224" t="inlineStr"/>
+      <c r="C54" s="224" t="inlineStr"/>
+      <c r="D54" s="224" t="inlineStr"/>
+      <c r="E54" s="224" t="inlineStr"/>
+      <c r="F54" s="224" t="inlineStr"/>
+      <c r="G54" s="224" t="inlineStr">
+        <is>
+          <t>Ronda HYROX 1 (pareja)</t>
+        </is>
+      </c>
+      <c r="H54" s="224" t="inlineStr">
+        <is>
+          <t>1 ronda fluida</t>
+        </is>
+      </c>
+      <c r="I54" s="224" t="inlineStr">
+        <is>
+          <t>800m Run pareja juntos (~5:30-5:50/km) -&gt; 1000m Ski Erg TOTAL pareja, ~500m cada uno con relevos -&gt; 25 WB 6kg TOTAL pareja ~12-13 cada uno -&gt; 20m Sled Push (un atleta lo completa, carga ligera-media) -&gt; 20m Sled Pull (un atleta lo completa, carga ligera) -&gt; 800m Row TOTAL pareja ~400m cada uno -&gt; 30 Lunges (un atleta los completa) -&gt; 30 Burpees pareja repartido. WB 6kg.</t>
+        </is>
+      </c>
+      <c r="J54" s="224" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="224" t="inlineStr"/>
+      <c r="B55" s="224" t="inlineStr"/>
+      <c r="C55" s="224" t="inlineStr"/>
+      <c r="D55" s="224" t="inlineStr"/>
+      <c r="E55" s="224" t="inlineStr"/>
+      <c r="F55" s="224" t="inlineStr"/>
+      <c r="G55" s="224" t="inlineStr">
+        <is>
+          <t>Ronda HYROX 2 (pareja)</t>
+        </is>
+      </c>
+      <c r="H55" s="224" t="inlineStr">
+        <is>
+          <t>1 ronda fluida</t>
+        </is>
+      </c>
+      <c r="I55" s="224" t="inlineStr">
+        <is>
+          <t>Igual estructura a ronda 1 · Desc 60–90'' entre rondas. Foco: incluir burpees esta vez (S3-D3 omitidos por calor).</t>
+        </is>
+      </c>
+      <c r="J55" s="224" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="224" t="inlineStr"/>
+      <c r="B56" s="224" t="inlineStr"/>
+      <c r="C56" s="224" t="inlineStr"/>
+      <c r="D56" s="224" t="inlineStr"/>
+      <c r="E56" s="224" t="inlineStr"/>
+      <c r="F56" s="224" t="inlineStr"/>
+      <c r="G56" s="224" t="inlineStr">
+        <is>
+          <t>Ronda HYROX 3 (pareja)</t>
+        </is>
+      </c>
+      <c r="H56" s="224" t="inlineStr">
+        <is>
+          <t>1 ronda fluida</t>
+        </is>
+      </c>
+      <c r="I56" s="224" t="inlineStr">
+        <is>
+          <t>Igual estructura · ritmo ligeramente mas sostenido si sensaciones permiten · WB 6kg</t>
+        </is>
+      </c>
+      <c r="J56" s="224" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="224" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B57" s="224" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="C57" s="224" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="D57" s="224" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E57" s="224" t="inlineStr">
+        <is>
+          <t>Sabado — Series carrera 8x400m · ~55'</t>
+        </is>
+      </c>
+      <c r="F57" s="224" t="inlineStr">
+        <is>
+          <t>RPE 7</t>
+        </is>
+      </c>
+      <c r="G57" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H57" s="224" t="inlineStr">
+        <is>
+          <t>1x10'</t>
+        </is>
+      </c>
+      <c r="I57" s="224" t="inlineStr">
+        <is>
+          <t>10' trote suave + tecnica de carrera (skipping, elevacion rodilla) + 3x100m progresivos</t>
+        </is>
+      </c>
+      <c r="J57" s="224" t="inlineStr">
+        <is>
+          <t>Baseline Excel S5-MK-D4 (8x400m @ 2:02–2:06/400m con rec 60–90''). AJUSTE: ritmo conservado a 2:08–2:12/400m con salida progresiva. S2-D4 series MK registro RPE 8 con caida pronunciada (1:40 -&gt; 2:28/400m equiv 4:10 -&gt; 6:10/km) y S3-D2 Z2 mostro caida similar. macro_meso_micro §S.G.A. — antes de pedir el ritmo Excel 5:05/km, consolidar el rango 5:20–5:30/km en S5 para mantener carga sin sobreentrenar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="224" t="inlineStr"/>
+      <c r="B58" s="224" t="inlineStr"/>
+      <c r="C58" s="224" t="inlineStr"/>
+      <c r="D58" s="224" t="inlineStr"/>
+      <c r="E58" s="224" t="inlineStr"/>
+      <c r="F58" s="224" t="inlineStr"/>
+      <c r="G58" s="224" t="inlineStr">
+        <is>
+          <t>Series 8x400m (Bateria C02)</t>
+        </is>
+      </c>
+      <c r="H58" s="224" t="inlineStr">
+        <is>
+          <t>8x400m</t>
+        </is>
+      </c>
+      <c r="I58" s="224" t="inlineStr">
+        <is>
+          <t>Ritmo 2:08–2:12/400m (5:20–5:30/km) · Rec 60–90'' caminando entre series · Salida conservadora arrancando en 2:12 los 2 primeros, bajar progresivamente</t>
+        </is>
+      </c>
+      <c r="J58" s="224" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="224" t="inlineStr"/>
+      <c r="B59" s="224" t="inlineStr"/>
+      <c r="C59" s="224" t="inlineStr"/>
+      <c r="D59" s="224" t="inlineStr"/>
+      <c r="E59" s="224" t="inlineStr"/>
+      <c r="F59" s="224" t="inlineStr"/>
+      <c r="G59" s="224" t="inlineStr">
+        <is>
+          <t>Vuelta a la calma</t>
+        </is>
+      </c>
+      <c r="H59" s="224" t="inlineStr">
+        <is>
+          <t>1x5'</t>
+        </is>
+      </c>
+      <c r="I59" s="224" t="inlineStr">
+        <is>
+          <t>Trote muy suave + estiramientos dinamicos</t>
+        </is>
+      </c>
+      <c r="J59" s="224" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="223" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B60" s="223" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C60" s="223" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D60" s="223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="223" t="inlineStr">
+        <is>
+          <t>Nota semanal</t>
+        </is>
+      </c>
+      <c r="F60" s="223" t="inlineStr"/>
+      <c r="G60" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S5 Base Aerobica · 4 dias · RPE objetivo 7-8 · 65-70% RM · 'Subir umbral'. ANALISIS REGISTROS COMPLETO Xabi: S1 0 sesiones (decision acompañando a MK con fiebre). S2-D3 HYROX RPE 5 con remo 1:55/500m, ski 2:20/500m, falta de aire. S2-D4 series RPE 7 (1:26/400m primera, mejorar respiracion). S3-D1 fuerza RPE 3 — MUY HOLGADO, por debajo del objetivo de fase. S3-D2 Z2 RPE 8 (objetivo 6, +2 puntos). S3-D3 HYROX RPE 7 OK. AJUSTES S5: subir ligeramente volumen fuerza (añadir Press Banca + extender trineo) dado RPE 3 holgado en S3-D1 — Tema 7 §sobrecarga progresiva sugiere que Xabi tolera mas carga; </t>
+        </is>
+      </c>
+      <c r="H60" s="223" t="inlineStr"/>
+      <c r="I60" s="223" t="inlineStr"/>
+      <c r="J60" s="223" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="224" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B61" s="224" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C61" s="224" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D61" s="224" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E61" s="224" t="inlineStr">
+        <is>
+          <t>Miercoles — Fuerza + Trineo (volumen extendido) · ~65'</t>
+        </is>
+      </c>
+      <c r="F61" s="224" t="inlineStr">
+        <is>
+          <t>RPE 7-8</t>
+        </is>
+      </c>
+      <c r="G61" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H61" s="224" t="inlineStr">
+        <is>
+          <t>1x5'</t>
+        </is>
+      </c>
+      <c r="I61" s="224" t="inlineStr">
+        <is>
+          <t>5' Assault Bike + movilidad dinamica + 2r activacion (goblet + hip hinge)</t>
+        </is>
+      </c>
+      <c r="J61" s="224" t="inlineStr">
+        <is>
+          <t>Baseline Excel S5-Xabi-D1 (Sentadilla 4x5 @70%-&gt;42.5kg, PM 4x4 @75%-&gt;60kg, Trineo 4x20m, Core 3x30''). AJUSTES: añadido Press Banca @70%-&gt;63kg + extender Trineo 20m-&gt;25m + plancha 30''-&gt;40'' (cita Tema 7 §sobrecarga progresiva). S3-D1 Xabi RPE real = 3 con cargas baseline anteriores: muy por debajo del objetivo de fase (RPE 7-8). El atleta tolera mas; añadir volumen es prudente sin saltarse a cargas supra-HYROX (que solo aplicarian desde S13 Realizacion segun regla 9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="224" t="inlineStr"/>
+      <c r="B62" s="224" t="inlineStr"/>
+      <c r="C62" s="224" t="inlineStr"/>
+      <c r="D62" s="224" t="inlineStr"/>
+      <c r="E62" s="224" t="inlineStr"/>
+      <c r="F62" s="224" t="inlineStr"/>
+      <c r="G62" s="224" t="inlineStr">
+        <is>
+          <t>Sentadilla (Bateria F01)</t>
+        </is>
+      </c>
+      <c r="H62" s="224" t="inlineStr">
+        <is>
+          <t>4x5</t>
+        </is>
+      </c>
+      <c r="I62" s="224" t="inlineStr">
+        <is>
+          <t>@70% RM -&gt; 42.5kg · Desc 60–90''</t>
+        </is>
+      </c>
+      <c r="J62" s="224" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="224" t="inlineStr"/>
+      <c r="B63" s="224" t="inlineStr"/>
+      <c r="C63" s="224" t="inlineStr"/>
+      <c r="D63" s="224" t="inlineStr"/>
+      <c r="E63" s="224" t="inlineStr"/>
+      <c r="F63" s="224" t="inlineStr"/>
+      <c r="G63" s="224" t="inlineStr">
+        <is>
+          <t>Peso Muerto (Bateria F02)</t>
+        </is>
+      </c>
+      <c r="H63" s="224" t="inlineStr">
+        <is>
+          <t>4x4</t>
+        </is>
+      </c>
+      <c r="I63" s="224" t="inlineStr">
+        <is>
+          <t>@75% RM -&gt; 60kg · Desc 60–90''</t>
+        </is>
+      </c>
+      <c r="J63" s="224" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="224" t="inlineStr"/>
+      <c r="B64" s="224" t="inlineStr"/>
+      <c r="C64" s="224" t="inlineStr"/>
+      <c r="D64" s="224" t="inlineStr"/>
+      <c r="E64" s="224" t="inlineStr"/>
+      <c r="F64" s="224" t="inlineStr"/>
+      <c r="G64" s="224" t="inlineStr">
+        <is>
+          <t>Press Banca (Bateria F03)</t>
+        </is>
+      </c>
+      <c r="H64" s="224" t="inlineStr">
+        <is>
+          <t>3x6</t>
+        </is>
+      </c>
+      <c r="I64" s="224" t="inlineStr">
+        <is>
+          <t>@70% RM -&gt; 63kg · Desc 60–90'' — accesorio añadido dado RPE 3 holgado en S3-D1</t>
+        </is>
+      </c>
+      <c r="J64" s="224" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="224" t="inlineStr"/>
+      <c r="B65" s="224" t="inlineStr"/>
+      <c r="C65" s="224" t="inlineStr"/>
+      <c r="D65" s="224" t="inlineStr"/>
+      <c r="E65" s="224" t="inlineStr"/>
+      <c r="F65" s="224" t="inlineStr"/>
+      <c r="G65" s="224" t="inlineStr">
+        <is>
+          <t>Trineo Push + Pull (Bateria H03/H04)</t>
+        </is>
+      </c>
+      <c r="H65" s="224" t="inlineStr">
+        <is>
+          <t>4x25m Push + 4x25m Pull</t>
+        </is>
+      </c>
+      <c r="I65" s="224" t="inlineStr">
+        <is>
+          <t>Carga media-alta (Xabi extendio en S3-D1 a 100kg+ con holgura) · 5m extra vs baseline para añadir estimulo</t>
+        </is>
+      </c>
+      <c r="J65" s="224" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="224" t="inlineStr"/>
+      <c r="B66" s="224" t="inlineStr"/>
+      <c r="C66" s="224" t="inlineStr"/>
+      <c r="D66" s="224" t="inlineStr"/>
+      <c r="E66" s="224" t="inlineStr"/>
+      <c r="F66" s="224" t="inlineStr"/>
+      <c r="G66" s="224" t="inlineStr">
+        <is>
+          <t>Core — Plancha (Bateria R01)</t>
+        </is>
+      </c>
+      <c r="H66" s="224" t="inlineStr">
+        <is>
+          <t>3x40''</t>
+        </is>
+      </c>
+      <c r="I66" s="224" t="inlineStr">
+        <is>
+          <t>BW · Desc 45'' — +10'' vs baseline dado margen</t>
+        </is>
+      </c>
+      <c r="J66" s="224" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="224" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B67" s="224" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C67" s="224" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D67" s="224" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E67" s="224" t="inlineStr">
+        <is>
+          <t>Jueves — Carrera Z2 conservadora con foco respiratorio · ~55-60'</t>
+        </is>
+      </c>
+      <c r="F67" s="224" t="inlineStr">
+        <is>
+          <t>RPE 6</t>
+        </is>
+      </c>
+      <c r="G67" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H67" s="224" t="inlineStr">
+        <is>
+          <t>1x10'</t>
+        </is>
+      </c>
+      <c r="I67" s="224" t="inlineStr">
+        <is>
+          <t>5' movilidad + 5' trote muy suave</t>
+        </is>
+      </c>
+      <c r="J67" s="224" t="inlineStr">
+        <is>
+          <t>Baseline Excel S5-Xabi-D2 (55–65 min, comodo). AJUSTE: ritmo conservado 6:00–6:20/km dado S3-D2 RPE 8 vs objetivo 6 (+2 puntos). Notas recurrentes sobre falta de aire en S2-D3 y S2-D4 indican patron cronico — sesion como ventana para entrenar patron respiratorio antes de subir intensidad. Tema 6 §interferencia AMPK/mTOR — bajar intensidad concurrente tras fuerza extendida del miercoles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="224" t="inlineStr"/>
+      <c r="B68" s="224" t="inlineStr"/>
+      <c r="C68" s="224" t="inlineStr"/>
+      <c r="D68" s="224" t="inlineStr"/>
+      <c r="E68" s="224" t="inlineStr"/>
+      <c r="F68" s="224" t="inlineStr"/>
+      <c r="G68" s="224" t="inlineStr">
+        <is>
+          <t>Carrera continua Z2 (Bateria C01)</t>
+        </is>
+      </c>
+      <c r="H68" s="224" t="inlineStr">
+        <is>
+          <t>1x55 min</t>
+        </is>
+      </c>
+      <c r="I68" s="224" t="inlineStr">
+        <is>
+          <t>Ritmo 6:00–6:20/km · FC &lt;75% FCmax · comodo · FOCO RESPIRACION (zona cronica en notas: S2-D3 'falta de aire', S2-D4 'mejorar control respiratorio'). Inhalar 3 pasos / exhalar 3 pasos sostenido.</t>
+        </is>
+      </c>
+      <c r="J68" s="224" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="224" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B69" s="224" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C69" s="224" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D69" s="224" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E69" s="224" t="inlineStr">
+        <is>
+          <t>Viernes — HYROX Especifico (pareja) · ~60'</t>
+        </is>
+      </c>
+      <c r="F69" s="224" t="inlineStr">
+        <is>
+          <t>RPE 7</t>
+        </is>
+      </c>
+      <c r="G69" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H69" s="224" t="inlineStr">
+        <is>
+          <t>1x8'</t>
+        </is>
+      </c>
+      <c r="I69" s="224" t="inlineStr">
+        <is>
+          <t>8' Ski o Remo suave amortiguador 5-6 + movilidad hombro + 10 Wall Balls 6kg</t>
+        </is>
+      </c>
+      <c r="J69" s="224" t="inlineStr">
+        <is>
+          <t>Baseline Excel S5-Xabi-D3 (3 rondas HYROX juntos). Distancias TOTAL pareja segun Rulebook Doubles §6 (Ski/Row/WB repartidos; Sled Push/Pull y Lunges = un atleta los completa). S3-D3 RPE 7 OK. Foco especifico para Xabi: respiracion bajo carga (S2-D3 1:55/500m remo y 2:20/500m ski con falta de aire — mejorar ritmo respiratorio en transiciones, cita Bateria §H02 Remo: drive con piernas primero, exhala fuerte al final del recorrido).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="224" t="inlineStr"/>
+      <c r="B70" s="224" t="inlineStr"/>
+      <c r="C70" s="224" t="inlineStr"/>
+      <c r="D70" s="224" t="inlineStr"/>
+      <c r="E70" s="224" t="inlineStr"/>
+      <c r="F70" s="224" t="inlineStr"/>
+      <c r="G70" s="224" t="inlineStr">
+        <is>
+          <t>Ronda HYROX 1 (pareja)</t>
+        </is>
+      </c>
+      <c r="H70" s="224" t="inlineStr">
+        <is>
+          <t>1 ronda fluida</t>
+        </is>
+      </c>
+      <c r="I70" s="224" t="inlineStr">
+        <is>
+          <t>800m Run pareja juntos -&gt; 1000m Ski Erg TOTAL pareja ~500m cada uno con relevos (Xabi foco respiracion en remo/ski por patron S2-D3) -&gt; 25 WB 6kg TOTAL pareja -&gt; 20m Sled Push (un atleta) carga media -&gt; 20m Sled Pull (un atleta) -&gt; 800m Row TOTAL pareja -&gt; 30 Lunges (un atleta) -&gt; 30 Burpees pareja. WB 6kg.</t>
+        </is>
+      </c>
+      <c r="J70" s="224" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="224" t="inlineStr"/>
+      <c r="B71" s="224" t="inlineStr"/>
+      <c r="C71" s="224" t="inlineStr"/>
+      <c r="D71" s="224" t="inlineStr"/>
+      <c r="E71" s="224" t="inlineStr"/>
+      <c r="F71" s="224" t="inlineStr"/>
+      <c r="G71" s="224" t="inlineStr">
+        <is>
+          <t>Ronda HYROX 2 (pareja)</t>
+        </is>
+      </c>
+      <c r="H71" s="224" t="inlineStr">
+        <is>
+          <t>1 ronda fluida</t>
+        </is>
+      </c>
+      <c r="I71" s="224" t="inlineStr">
+        <is>
+          <t>Igual estructura · Desc 60–90'' entre rondas</t>
+        </is>
+      </c>
+      <c r="J71" s="224" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="224" t="inlineStr"/>
+      <c r="B72" s="224" t="inlineStr"/>
+      <c r="C72" s="224" t="inlineStr"/>
+      <c r="D72" s="224" t="inlineStr"/>
+      <c r="E72" s="224" t="inlineStr"/>
+      <c r="F72" s="224" t="inlineStr"/>
+      <c r="G72" s="224" t="inlineStr">
+        <is>
+          <t>Ronda HYROX 3 (pareja)</t>
+        </is>
+      </c>
+      <c r="H72" s="224" t="inlineStr">
+        <is>
+          <t>1 ronda fluida</t>
+        </is>
+      </c>
+      <c r="I72" s="224" t="inlineStr">
+        <is>
+          <t>Igual estructura · ritmo ligeramente mas sostenido si sensaciones lo permiten</t>
+        </is>
+      </c>
+      <c r="J72" s="224" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="224" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B73" s="224" t="inlineStr">
+        <is>
+          <t>Xabi</t>
+        </is>
+      </c>
+      <c r="C73" s="224" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="D73" s="224" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E73" s="224" t="inlineStr">
+        <is>
+          <t>Sabado — Series carrera 8x400m · ~55'</t>
+        </is>
+      </c>
+      <c r="F73" s="224" t="inlineStr">
+        <is>
+          <t>RPE 7</t>
+        </is>
+      </c>
+      <c r="G73" s="224" t="inlineStr">
+        <is>
+          <t>Calentamiento</t>
+        </is>
+      </c>
+      <c r="H73" s="224" t="inlineStr">
+        <is>
+          <t>1x10'</t>
+        </is>
+      </c>
+      <c r="I73" s="224" t="inlineStr">
+        <is>
+          <t>10' trote suave + tecnica + 3x100m progresivos</t>
+        </is>
+      </c>
+      <c r="J73" s="224" t="inlineStr">
+        <is>
+          <t>Baseline Excel S5-Xabi-D4 (8x400m progresivo a su ritmo). Xabi S2-D4 RPE 7 a 1:26/400m: el ritmo objetivo S5 se modela a 1:28–1:32/400m con salida progresiva. macro_meso_micro §S.G.A. — mantener volumen 8x400m del baseline; ritmo controlado evita sobreentrenamiento aerobico dado RPE 8 en Z2 reciente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="224" t="inlineStr"/>
+      <c r="B74" s="224" t="inlineStr"/>
+      <c r="C74" s="224" t="inlineStr"/>
+      <c r="D74" s="224" t="inlineStr"/>
+      <c r="E74" s="224" t="inlineStr"/>
+      <c r="F74" s="224" t="inlineStr"/>
+      <c r="G74" s="224" t="inlineStr">
+        <is>
+          <t>Series 8x400m (Bateria C02)</t>
+        </is>
+      </c>
+      <c r="H74" s="224" t="inlineStr">
+        <is>
+          <t>8x400m</t>
+        </is>
+      </c>
+      <c r="I74" s="224" t="inlineStr">
+        <is>
+          <t>Ritmo 1:28–1:32/400m progresivo (Xabi mejor ritmo que MK, S2-D4 logró 1:26 RPE 7) · Rec 60–90'' caminando · FOCO RESPIRACION cada serie, inhalar 2 pasos / exhalar 2 pasos en serie · Salida conservadora 1:32 las 2 primeras, bajar a 1:28 las ultimas</t>
+        </is>
+      </c>
+      <c r="J74" s="224" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="224" t="inlineStr"/>
+      <c r="B75" s="224" t="inlineStr"/>
+      <c r="C75" s="224" t="inlineStr"/>
+      <c r="D75" s="224" t="inlineStr"/>
+      <c r="E75" s="224" t="inlineStr"/>
+      <c r="F75" s="224" t="inlineStr"/>
+      <c r="G75" s="224" t="inlineStr">
+        <is>
+          <t>Vuelta a la calma</t>
+        </is>
+      </c>
+      <c r="H75" s="224" t="inlineStr">
+        <is>
+          <t>1x5'</t>
+        </is>
+      </c>
+      <c r="I75" s="224" t="inlineStr">
+        <is>
+          <t>Trote muy suave + estiramientos dinamicos</t>
+        </is>
+      </c>
+      <c r="J75" s="224" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="FFE94560"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="1.54296875" customWidth="1" min="1" max="1"/>
@@ -32598,6 +35683,11 @@
           <t>Notas tecnicas</t>
         </is>
       </c>
+      <c r="L5" s="225" t="inlineStr">
+        <is>
+          <t>Usado en sesiones</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="19.5" customHeight="1">
       <c r="B6" s="190" t="inlineStr">
@@ -32650,6 +35740,11 @@
           <t>Rodillas alineadas · Bajar hasta paralelo</t>
         </is>
       </c>
+      <c r="L6" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="19.5" customHeight="1">
       <c r="B7" s="190" t="inlineStr">
@@ -32702,6 +35797,11 @@
           <t>Barra pegada al cuerpo · Cadera empuja al subir</t>
         </is>
       </c>
+      <c r="L7" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="19.5" customHeight="1">
       <c r="B8" s="190" t="inlineStr">
@@ -32754,6 +35854,11 @@
           <t>Escapulas retraidas · Bajar hasta pecho</t>
         </is>
       </c>
+      <c r="L8" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="B9" s="190" t="inlineStr">
@@ -32806,6 +35911,11 @@
           <t>Bisagra de cadera · Ligera flexion rodilla</t>
         </is>
       </c>
+      <c r="L9" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="B10" s="190" t="inlineStr">
@@ -32858,6 +35968,11 @@
           <t>Espalda alta apoyada en banco</t>
         </is>
       </c>
+      <c r="L10" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
       <c r="B11" s="190" t="inlineStr">
@@ -32910,6 +36025,11 @@
           <t>Rodilla trasera rozando suelo</t>
         </is>
       </c>
+      <c r="L11" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="B12" s="190" t="inlineStr">
@@ -32962,6 +36082,11 @@
           <t>Nucleo activado · No arquear lumbar</t>
         </is>
       </c>
+      <c r="L12" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
       <c r="B13" s="190" t="inlineStr">
@@ -33014,6 +36139,11 @@
           <t>Codos pegados al cuerpo</t>
         </is>
       </c>
+      <c r="L13" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="B14" s="190" t="inlineStr">
@@ -33066,6 +36196,11 @@
           <t>Codo completo al inicio</t>
         </is>
       </c>
+      <c r="L14" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="B15" s="190" t="inlineStr">
@@ -33118,6 +36253,11 @@
           <t>Codos altos · Manos a la cara</t>
         </is>
       </c>
+      <c r="L15" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="B16" s="195" t="inlineStr">
@@ -33170,6 +36310,11 @@
           <t>Cadera neutra</t>
         </is>
       </c>
+      <c r="L16" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="B17" s="200" t="inlineStr">
@@ -33222,6 +36367,11 @@
           <t>Traccion doble brazo</t>
         </is>
       </c>
+      <c r="L17" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="B18" s="200" t="inlineStr">
@@ -33274,6 +36424,11 @@
           <t>Drive con piernas primero</t>
         </is>
       </c>
+      <c r="L18" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="B19" s="200" t="inlineStr">
@@ -33326,6 +36481,11 @@
           <t>Pasos cortos · Cuerpo ~45°</t>
         </is>
       </c>
+      <c r="L19" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="B20" s="200" t="inlineStr">
@@ -33378,6 +36538,11 @@
           <t>Caminar hacia atras · Cuerda tensa</t>
         </is>
       </c>
+      <c r="L20" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="B21" s="200" t="inlineStr">
@@ -33430,6 +36595,11 @@
           <t>Salto largo · Aterrizaje suave</t>
         </is>
       </c>
+      <c r="L21" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="B22" s="200" t="inlineStr">
@@ -33482,6 +36652,11 @@
           <t>Hombros atras · Pasos cortos</t>
         </is>
       </c>
+      <c r="L22" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="B23" s="200" t="inlineStr">
@@ -33534,6 +36709,11 @@
           <t>Rodilla trasera 1cm del suelo</t>
         </is>
       </c>
+      <c r="L23" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="B24" s="200" t="inlineStr">
@@ -33586,6 +36766,11 @@
           <t>Diana a 3m · Squat profundo</t>
         </is>
       </c>
+      <c r="L24" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="B25" s="205" t="inlineStr">
@@ -33638,6 +36823,11 @@
           <t>Hablar sin problema · FC &lt; 75% FCmax</t>
         </is>
       </c>
+      <c r="L25" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="19.5" customHeight="1">
       <c r="B26" s="205" t="inlineStr">
@@ -33690,6 +36880,11 @@
           <t>Rec. 60-120'' · Salida conservadora</t>
         </is>
       </c>
+      <c r="L26" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="B27" s="205" t="inlineStr">
@@ -33742,6 +36937,11 @@
           <t>Ritmo estable</t>
         </is>
       </c>
+      <c r="L27" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="B28" s="205" t="inlineStr">
@@ -33794,6 +36994,11 @@
           <t>Ritmo constante cada repeticion</t>
         </is>
       </c>
+      <c r="L28" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="B29" s="205" t="inlineStr">
@@ -33846,6 +37051,11 @@
           <t>Sale del poli directo · Sin recuperacion previa</t>
         </is>
       </c>
+      <c r="L29" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="B30" s="210" t="inlineStr">
@@ -33898,6 +37108,11 @@
           <t>Cadera, tobillo, hombro · Antes de cada sesion</t>
         </is>
       </c>
+      <c r="L30" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="B31" s="210" t="inlineStr">
@@ -33948,6 +37163,11 @@
       <c r="K31" s="214" t="inlineStr">
         <is>
           <t>Elevacion rodilla · Zancada · Frecuencia</t>
+        </is>
+      </c>
+      <c r="L31" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí</t>
         </is>
       </c>
     </row>
@@ -34017,6 +37237,11 @@
           <t>KB colgado del empeine o tobillera. De pie, eleva la rodilla al pecho. Controla el equilibrio. Sin balanceo de tronco.</t>
         </is>
       </c>
+      <c r="L33" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="27.75" customHeight="1">
       <c r="B34" s="190" t="inlineStr">
@@ -34069,6 +37294,11 @@
           <t>KB colgado del pie. Sobre un escalon o step. Baja el talon por debajo del nivel, sube en puntilla. Rango completo.</t>
         </is>
       </c>
+      <c r="L34" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="27.75" customHeight="1">
       <c r="B35" s="190" t="inlineStr">
@@ -34121,6 +37351,11 @@
           <t>Mancuerna en posicion goblet (al pecho). Sube al cajon, al llegar arriba eleva la rodilla contraria al pecho. Alta transferencia a carrera y HYROX.</t>
         </is>
       </c>
+      <c r="L35" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="27.75" customHeight="1">
       <c r="B36" s="190" t="inlineStr">
@@ -34173,6 +37408,11 @@
           <t>Sobre un pie, preferiblemente en escalon para mayor rango. Sube en puntilla y baja lento (3-4 segundos). Clave para fuerza de propulsion en carrera.</t>
         </is>
       </c>
+      <c r="L36" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="27.75" customHeight="1">
       <c r="B37" s="190" t="inlineStr">
@@ -34223,6 +37463,11 @@
       <c r="K37" s="194" t="inlineStr">
         <is>
           <t>Sobre un pie, salto elastico en puntilla sobre step bajo. Contacto breve con el suelo, sin flexion de rodilla. Mejora reactividad y elasticidad para carrera.</t>
+        </is>
+      </c>
+      <c r="L37" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
         </is>
       </c>
     </row>
@@ -34292,6 +37537,11 @@
           <t>De pie, una rodilla a 90 al frente, la otra estirada atras, pies elevados. Pasa el KB de mano en mano por debajo del muslo elevado. Control total de la pelvis sin rotacion.</t>
         </is>
       </c>
+      <c r="L39" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="27.75" customHeight="1">
       <c r="B40" s="195" t="inlineStr">
@@ -34344,6 +37594,11 @@
           <t>En plancha (codos o manos). Eleva una pierna estirada manteniendo la cadera completamente estable. Sin rotacion de pelvis. Aguanta 2 segundos arriba.</t>
         </is>
       </c>
+      <c r="L40" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="27.75" customHeight="1">
       <c r="B41" s="195" t="inlineStr">
@@ -34396,6 +37651,11 @@
           <t>De pie lateral a la polea o goma. Manos al pecho, empuja recto al frente y regresa lento. La resistencia tira de ti para rotarte — resiste. Columna neutra en todo momento.</t>
         </is>
       </c>
+      <c r="L41" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="27.75" customHeight="1">
       <c r="B42" s="195" t="inlineStr">
@@ -34446,6 +37706,11 @@
       <c r="K42" s="199" t="inlineStr">
         <is>
           <t>Sostener KB en posicion fija. Variantes: al lado del cuerpo (farmer hold), a un lado (suitcase hold), en rack a hombro, o sobre cabeza (overhead hold). Cada variante tiene un estimulo diferente.</t>
+        </is>
+      </c>
+      <c r="L42" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
         </is>
       </c>
     </row>
@@ -34515,6 +37780,11 @@
           <t>Sentadilla frontal completa + press sobre cabeza en un solo movimiento continuo. Sin pausa en la subida. Alta demanda metabolica. Tipico en CrossFit y circuitos HYROX.</t>
         </is>
       </c>
+      <c r="L44" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí (S10+)</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="27.75" customHeight="1">
       <c r="B45" s="190" t="inlineStr">
@@ -34567,6 +37837,11 @@
           <t>Desde rack frontal. Pequeno dip de rodillas (10-15 cm) y extension explosiva para iniciar el movimiento. Empuja hasta extension completa. Mas carga que press estricto.</t>
         </is>
       </c>
+      <c r="L45" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí (S10+)</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="27.75" customHeight="1">
       <c r="B46" s="190" t="inlineStr">
@@ -34619,6 +37894,11 @@
           <t>Desde el suelo o desde swing. En un movimiento continuo, lleva el KB a extension completa sobre la cabeza con el brazo vertical. Munica el KB — no frenes con el biceps. Confirma si usas barra o KB.</t>
         </is>
       </c>
+      <c r="L46" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí (S10+)</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="27.75" customHeight="1">
       <c r="B47" s="190" t="inlineStr">
@@ -34671,6 +37951,11 @@
           <t>Bisagra de cadera explosiva. La carga sube por la fuerza de la cadera, no de los brazos. Dos variantes: swing americano (hasta sobre la cabeza) o ruso (hasta altura de hombros). Espalda recta en todo momento.</t>
         </is>
       </c>
+      <c r="L47" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí (S10+)</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="27.75" customHeight="1">
       <c r="B48" s="190" t="inlineStr">
@@ -34721,6 +38006,11 @@
       <c r="K48" s="194" t="inlineStr">
         <is>
           <t>Burpee con las manos en las mancuernas + al subir, swing-snatch de ambas mancuernas hasta sobre la cabeza en un movimiento. Alta demanda cardiovascular y de hombros.</t>
+        </is>
+      </c>
+      <c r="L48" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí (S10+)</t>
         </is>
       </c>
     </row>
@@ -34790,6 +38080,11 @@
           <t>Burpee estandar pero aterriza con los dos pies sobre un disco en el suelo. Variante de potencia. Simula el gesto del Burpee Broad Jump de HYROX.</t>
         </is>
       </c>
+      <c r="L50" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí (S10+)</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="27.75" customHeight="1">
       <c r="B51" s="205" t="inlineStr">
@@ -34840,6 +38135,11 @@
       <c r="K51" s="209" t="inlineStr">
         <is>
           <t>Rondas de carrera en cinta (&lt;1 km) combinadas con ejercicios de gym. Ejemplo: 400m cinta + 10 Thrusters + 20 KB swings + 10 Burpees. Descanso entre rondas 90-120''. Util cuando la calle no es viable.</t>
+        </is>
+      </c>
+      <c r="L51" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
         </is>
       </c>
     </row>
@@ -34907,6 +38207,11 @@
       <c r="K53" s="204" t="inlineStr">
         <is>
           <t>Paso hacia adelante, rodilla trasera baja hasta 1 cm del suelo, vuelve al centro. Sin desplazamiento. Mas tension en cuadriceps que la version caminando.</t>
+        </is>
+      </c>
+      <c r="L53" s="226" t="inlineStr">
+        <is>
+          <t>✓ Sí (S10+)</t>
         </is>
       </c>
     </row>
@@ -35283,6 +38588,11 @@
           <t>Salto vertical bilateral al cajon. Aterrizaje suave en cuarto de sentadilla. Bajar caminando. Transferencia directa a Burpee Broad Jump.</t>
         </is>
       </c>
+      <c r="L65" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -35335,6 +38645,11 @@
           <t>Salto horizontal maximo a dos pies, 5 saltos seguidos sin descanso. Especifico para BBJ HYROX.</t>
         </is>
       </c>
+      <c r="L66" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -35387,6 +38702,11 @@
           <t>Desde el suelo, lleva la barra hasta hombros en un movimiento explosivo. Tecnica critica — empieza ligero. Potencia transferible a Sled Push.</t>
         </is>
       </c>
+      <c r="L67" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -35439,6 +38759,11 @@
           <t>Levanta la pelota sobre la cabeza y estampala contra el suelo con fuerza maxima. Descarga la fatiga acumulada y entrena el patron del Wall Ball.</t>
         </is>
       </c>
+      <c r="L68" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -35491,56 +38816,197 @@
           <t>KB swing tradicional con UNA SOLA mano. El core resiste la rotacion. Combinacion potencia cadera + antirotacion core.</t>
         </is>
       </c>
+      <c r="L69" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="B70" s="228" t="inlineStr">
         <is>
           <t>F27</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Banded Skater Hops</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>F Fuerza</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Gluteo medio, RFD lateral</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>3x8-10/lado</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>8-10/lado</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>Banda media</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>Saltos laterales con banda en muslos. Aterrizaje en una pierna, controlado. Mejora equilibrio dinamico para lunges y BBJ.</t>
+        </is>
+      </c>
+      <c r="L70" s="227" t="inlineStr">
+        <is>
+          <t>✗ No usado</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="232" t="inlineStr">
+        <is>
+          <t>Añadidos v11 (2026-06-02) — fuerza de tirón + grip específico HYROX</t>
+        </is>
+      </c>
+      <c r="C71" s="230" t="n"/>
+      <c r="D71" s="230" t="n"/>
+      <c r="E71" s="230" t="n"/>
+      <c r="F71" s="230" t="n"/>
+      <c r="G71" s="230" t="n"/>
+      <c r="H71" s="230" t="n"/>
+      <c r="I71" s="230" t="n"/>
+      <c r="J71" s="230" t="n"/>
+      <c r="K71" s="230" t="n"/>
+      <c r="L71" s="227" t="n"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="234" t="inlineStr">
+        <is>
+          <t>F28</t>
+        </is>
+      </c>
+      <c r="C72" s="234" t="inlineStr">
+        <is>
+          <t>Remo con Barra (Barbell Row)</t>
+        </is>
+      </c>
+      <c r="D72" s="234" t="inlineStr">
+        <is>
+          <t>F Fuerza</t>
+        </is>
+      </c>
+      <c r="E72" s="234" t="inlineStr">
+        <is>
+          <t>Dorsal, romboides, biceps, deltoides post.</t>
+        </is>
+      </c>
+      <c r="F72" s="234" t="inlineStr">
+        <is>
+          <t>4x6-10</t>
+        </is>
+      </c>
+      <c r="G72" s="234" t="inlineStr">
+        <is>
+          <t>6-10</t>
+        </is>
+      </c>
+      <c r="H72" s="234" t="inlineStr">
+        <is>
+          <t>Barra 30-60kg</t>
+        </is>
+      </c>
+      <c r="I72" s="234" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J72" s="234" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="234" t="inlineStr">
+        <is>
+          <t>Barra a la altura del pecho con presas prona. Espalda neutra, rodillas ligeramente flexionadas. Codos pegados, barra roza abdomen. Complementa Ski Erg y Remo maquina. Transferencia directa al Sled Pull.</t>
+        </is>
+      </c>
+      <c r="L72" s="233" t="inlineStr">
+        <is>
+          <t>✗ Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="229" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="C73" s="230" t="inlineStr">
+        <is>
+          <t>Dead Hang (Colgado de barra)</t>
+        </is>
+      </c>
+      <c r="D73" s="230" t="inlineStr">
+        <is>
+          <t>R Core</t>
+        </is>
+      </c>
+      <c r="E73" s="230" t="inlineStr">
+        <is>
+          <t>Grip, hombros, dorsal, descompresion lumbar</t>
+        </is>
+      </c>
+      <c r="F73" s="230" t="inlineStr">
+        <is>
+          <t>3x20-60s</t>
+        </is>
+      </c>
+      <c r="G73" s="230" t="inlineStr">
+        <is>
+          <t>20-60 seg</t>
+        </is>
+      </c>
+      <c r="H73" s="230" t="inlineStr">
+        <is>
+          <t>BW</t>
+        </is>
+      </c>
+      <c r="I73" s="230" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J73" s="230" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="230" t="inlineStr">
+        <is>
+          <t>Colgado de barra en agarre prono o neutro. Brazos completamente extendidos. Hombros activos (no hundir cuello). Progresion: Hang pasivo → activo (hombros deprimidos) → con peso. Clave para Farmer Carry y fuerza de agarre en race day.</t>
+        </is>
+      </c>
+      <c r="L73" s="233" t="inlineStr">
+        <is>
+          <t>✗ Nuevo</t>
         </is>
       </c>
     </row>
@@ -35560,13 +39026,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -35663,6 +39129,94 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>v9</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Agregadas hojas Registros (S1-S3 con RPE/notas/custom/extra) + Planes Confirmados (Claude) (S4-S5 MK+Xabi)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sincronizado con DB Supabase (registros + training_weeks status=confirmed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>v10-fix</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Vision Macro S3 corregida (off-by-one cols 10→11). Restaurado Objetivo.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MK 3/4 rpe 6.7 · Xabi 3/4 rpe 6.0 · Obs sesion-a-sesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>v11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1) HYROX 50/50 explícito: distancias divididas por atleta en MK y Xabi Plan (Ski/Row/BBJ/WB = mitad por persona; Sled/Farmer/Lunges = completo cada uno). 2) Batería: añadidos F28 (Remo con Barra) y R11 (Dead Hang). 3) Batería: columna "Usado en sesiones" — auditados todos los ejercicios. NO usados en sesiones actuales: F04, F05 (solo S1 Xabi), F06 (solo S1 Xabi), F12-F16 (unilaterales), F17-F21 (Thruster/Push Press/Snatch/KB Swing/Devils Press), R02-R05 (core anti-movimiento), H09 (Burpee to Plate), C06 (HIIT cinta), H10 (Zancada estática), F22-F27 (Box Jump/Broad Jump/Power Clean/Med Ball Slam/SA KB Swing/Banded Skater). 4) Nota sobrecarga S15 y S19: WB+2kg, Farmer+4kg, Sled+placa — entrenar más pesado que comp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>v12</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Integración ejercicios batería no usados: HIIT martes rotado por semana — S10: KB Swing+Thruster, S11: Push Press+Burpee to Plate, S13: KB Swing+Thruster, S14: Push Press+Burpee to Plate, S15: KB Swing+Devils Press, S16: KB Swing+Burpee to Plate, S18: Push Press+Snatch KB, S19: KB Swing+Burpee to Plate, S20: Push Press+WB. Viernes fuerza S13-S20: bloque potencia (+10 min) con KB Swing / Push Press / Snatch KB. Actualizada columna "Usado en sesiones" en Batería para F17-F21, H09, H10.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
